--- a/notebooks/cleaned_stock_prices.xlsx
+++ b/notebooks/cleaned_stock_prices.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>OGDC</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -475,7 +475,7 @@
         <v>48.82</v>
       </c>
       <c r="D2" t="n">
-        <v>5850</v>
+        <v>80.22</v>
       </c>
       <c r="E2" t="n">
         <v>100.7</v>
@@ -495,7 +495,7 @@
         <v>48.55</v>
       </c>
       <c r="D3" t="n">
-        <v>5850</v>
+        <v>79.94</v>
       </c>
       <c r="E3" t="n">
         <v>99.76000000000001</v>
@@ -515,7 +515,7 @@
         <v>48.22</v>
       </c>
       <c r="D4" t="n">
-        <v>5750</v>
+        <v>78.55</v>
       </c>
       <c r="E4" t="n">
         <v>98.86</v>
@@ -535,7 +535,7 @@
         <v>50.81</v>
       </c>
       <c r="D5" t="n">
-        <v>5610</v>
+        <v>79.77</v>
       </c>
       <c r="E5" t="n">
         <v>97.98</v>
@@ -555,7 +555,7 @@
         <v>50.71</v>
       </c>
       <c r="D6" t="n">
-        <v>5400.1</v>
+        <v>82.31</v>
       </c>
       <c r="E6" t="n">
         <v>96.43000000000001</v>
@@ -575,7 +575,7 @@
         <v>48.57</v>
       </c>
       <c r="D7" t="n">
-        <v>5600</v>
+        <v>84.83</v>
       </c>
       <c r="E7" t="n">
         <v>95.05</v>
@@ -595,7 +595,7 @@
         <v>49.05</v>
       </c>
       <c r="D8" t="n">
-        <v>5600.1</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="E8" t="n">
         <v>95.15000000000001</v>
@@ -615,7 +615,7 @@
         <v>48.81</v>
       </c>
       <c r="D9" t="n">
-        <v>5600.1</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="E9" t="n">
         <v>94.52</v>
@@ -635,7 +635,7 @@
         <v>49.26</v>
       </c>
       <c r="D10" t="n">
-        <v>5850</v>
+        <v>86.77</v>
       </c>
       <c r="E10" t="n">
         <v>94.11</v>
@@ -655,7 +655,7 @@
         <v>48.75</v>
       </c>
       <c r="D11" t="n">
-        <v>5650</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>93.33</v>
@@ -675,7 +675,7 @@
         <v>48.1</v>
       </c>
       <c r="D12" t="n">
-        <v>5399</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="E12" t="n">
         <v>92.88</v>
@@ -695,7 +695,7 @@
         <v>45.48</v>
       </c>
       <c r="D13" t="n">
-        <v>5595</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="E13" t="n">
         <v>89.04000000000001</v>
@@ -715,7 +715,7 @@
         <v>44.74</v>
       </c>
       <c r="D14" t="n">
-        <v>5308</v>
+        <v>76.09</v>
       </c>
       <c r="E14" t="n">
         <v>90.12</v>
@@ -735,7 +735,7 @@
         <v>45.11</v>
       </c>
       <c r="D15" t="n">
-        <v>5260</v>
+        <v>79.44</v>
       </c>
       <c r="E15" t="n">
         <v>89.62</v>
@@ -755,7 +755,7 @@
         <v>45.82</v>
       </c>
       <c r="D16" t="n">
-        <v>5310</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="E16" t="n">
         <v>88.3</v>
@@ -775,7 +775,7 @@
         <v>45.2</v>
       </c>
       <c r="D17" t="n">
-        <v>5190.01</v>
+        <v>81.72</v>
       </c>
       <c r="E17" t="n">
         <v>88.27</v>
@@ -795,7 +795,7 @@
         <v>45.43</v>
       </c>
       <c r="D18" t="n">
-        <v>5190</v>
+        <v>84.5</v>
       </c>
       <c r="E18" t="n">
         <v>88.67</v>
@@ -815,7 +815,7 @@
         <v>46.13</v>
       </c>
       <c r="D19" t="n">
-        <v>5213</v>
+        <v>85.97</v>
       </c>
       <c r="E19" t="n">
         <v>89.73999999999999</v>
@@ -835,7 +835,7 @@
         <v>48.65</v>
       </c>
       <c r="D20" t="n">
-        <v>5324.99</v>
+        <v>86.3</v>
       </c>
       <c r="E20" t="n">
         <v>95.61</v>
@@ -855,7 +855,7 @@
         <v>48</v>
       </c>
       <c r="D21" t="n">
-        <v>5280</v>
+        <v>86.64</v>
       </c>
       <c r="E21" t="n">
         <v>93</v>
@@ -875,7 +875,7 @@
         <v>48</v>
       </c>
       <c r="D22" t="n">
-        <v>5160</v>
+        <v>86.27</v>
       </c>
       <c r="E22" t="n">
         <v>91.65000000000001</v>
@@ -895,7 +895,7 @@
         <v>48.24</v>
       </c>
       <c r="D23" t="n">
-        <v>5275</v>
+        <v>87.8</v>
       </c>
       <c r="E23" t="n">
         <v>92.48</v>
@@ -915,7 +915,7 @@
         <v>48.2</v>
       </c>
       <c r="D24" t="n">
-        <v>5205.01</v>
+        <v>87.3</v>
       </c>
       <c r="E24" t="n">
         <v>93.02</v>
@@ -935,7 +935,7 @@
         <v>48.2</v>
       </c>
       <c r="D25" t="n">
-        <v>5300</v>
+        <v>87.02</v>
       </c>
       <c r="E25" t="n">
         <v>92.53</v>
@@ -955,7 +955,7 @@
         <v>47.97</v>
       </c>
       <c r="D26" t="n">
-        <v>5364</v>
+        <v>85.94</v>
       </c>
       <c r="E26" t="n">
         <v>91.55</v>
@@ -975,7 +975,7 @@
         <v>47.47</v>
       </c>
       <c r="D27" t="n">
-        <v>5299.99</v>
+        <v>92.38</v>
       </c>
       <c r="E27" t="n">
         <v>92.5</v>
@@ -995,7 +995,7 @@
         <v>46.25</v>
       </c>
       <c r="D28" t="n">
-        <v>5338.99</v>
+        <v>99.3</v>
       </c>
       <c r="E28" t="n">
         <v>94.03</v>
@@ -1015,7 +1015,7 @@
         <v>49.56</v>
       </c>
       <c r="D29" t="n">
-        <v>5315</v>
+        <v>99.78</v>
       </c>
       <c r="E29" t="n">
         <v>94.09999999999999</v>
@@ -1035,7 +1035,7 @@
         <v>49.48</v>
       </c>
       <c r="D30" t="n">
-        <v>5534.99</v>
+        <v>105.95</v>
       </c>
       <c r="E30" t="n">
         <v>96.64</v>
@@ -1055,7 +1055,7 @@
         <v>49.96</v>
       </c>
       <c r="D31" t="n">
-        <v>5441.67</v>
+        <v>101.06</v>
       </c>
       <c r="E31" t="n">
         <v>94.95999999999999</v>
@@ -1075,7 +1075,7 @@
         <v>50.31</v>
       </c>
       <c r="D32" t="n">
-        <v>5450</v>
+        <v>98.8</v>
       </c>
       <c r="E32" t="n">
         <v>94.43000000000001</v>
@@ -1095,7 +1095,7 @@
         <v>52.04</v>
       </c>
       <c r="D33" t="n">
-        <v>5399</v>
+        <v>93.94</v>
       </c>
       <c r="E33" t="n">
         <v>94.45</v>
@@ -1115,7 +1115,7 @@
         <v>51.86</v>
       </c>
       <c r="D34" t="n">
-        <v>5354.95</v>
+        <v>95.78</v>
       </c>
       <c r="E34" t="n">
         <v>92.40000000000001</v>
@@ -1135,7 +1135,7 @@
         <v>53.37</v>
       </c>
       <c r="D35" t="n">
-        <v>5381.05</v>
+        <v>93.37</v>
       </c>
       <c r="E35" t="n">
         <v>96.63</v>
@@ -1155,7 +1155,7 @@
         <v>56.31</v>
       </c>
       <c r="D36" t="n">
-        <v>5381.05</v>
+        <v>94.58</v>
       </c>
       <c r="E36" t="n">
         <v>97.09</v>
@@ -1175,7 +1175,7 @@
         <v>58.23</v>
       </c>
       <c r="D37" t="n">
-        <v>5399</v>
+        <v>89.72</v>
       </c>
       <c r="E37" t="n">
         <v>95.33</v>
@@ -1195,7 +1195,7 @@
         <v>55.96</v>
       </c>
       <c r="D38" t="n">
-        <v>5399</v>
+        <v>91.23</v>
       </c>
       <c r="E38" t="n">
         <v>95.95999999999999</v>
@@ -1215,7 +1215,7 @@
         <v>54.93</v>
       </c>
       <c r="D39" t="n">
-        <v>5314</v>
+        <v>90.78</v>
       </c>
       <c r="E39" t="n">
         <v>95.78</v>
@@ -1235,7 +1235,7 @@
         <v>54.35</v>
       </c>
       <c r="D40" t="n">
-        <v>5300</v>
+        <v>88.63</v>
       </c>
       <c r="E40" t="n">
         <v>95.03</v>
@@ -1255,7 +1255,7 @@
         <v>55.43</v>
       </c>
       <c r="D41" t="n">
-        <v>5300</v>
+        <v>87.66</v>
       </c>
       <c r="E41" t="n">
         <v>94.56999999999999</v>
@@ -1275,7 +1275,7 @@
         <v>52.69</v>
       </c>
       <c r="D42" t="n">
-        <v>5300</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="E42" t="n">
         <v>94.04000000000001</v>
@@ -1295,7 +1295,7 @@
         <v>52.5</v>
       </c>
       <c r="D43" t="n">
-        <v>5240</v>
+        <v>82.62</v>
       </c>
       <c r="E43" t="n">
         <v>94.93000000000001</v>
@@ -1315,7 +1315,7 @@
         <v>51.6</v>
       </c>
       <c r="D44" t="n">
-        <v>5464</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="E44" t="n">
         <v>95</v>
@@ -1335,7 +1335,7 @@
         <v>50.55</v>
       </c>
       <c r="D45" t="n">
-        <v>5299.78</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="E45" t="n">
         <v>97.09999999999999</v>
@@ -1355,7 +1355,7 @@
         <v>50.5</v>
       </c>
       <c r="D46" t="n">
-        <v>5400</v>
+        <v>88.12</v>
       </c>
       <c r="E46" t="n">
         <v>100.14</v>
@@ -1375,7 +1375,7 @@
         <v>54.28</v>
       </c>
       <c r="D47" t="n">
-        <v>5266.03</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="E47" t="n">
         <v>99.54000000000001</v>
@@ -1395,7 +1395,7 @@
         <v>52.98</v>
       </c>
       <c r="D48" t="n">
-        <v>5265</v>
+        <v>85.3</v>
       </c>
       <c r="E48" t="n">
         <v>98.19</v>
@@ -1415,7 +1415,7 @@
         <v>52.32</v>
       </c>
       <c r="D49" t="n">
-        <v>5495</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="E49" t="n">
         <v>97.77</v>
@@ -1435,7 +1435,7 @@
         <v>53.34</v>
       </c>
       <c r="D50" t="n">
-        <v>5495</v>
+        <v>87.19</v>
       </c>
       <c r="E50" t="n">
         <v>98.16</v>
@@ -1455,7 +1455,7 @@
         <v>53.4</v>
       </c>
       <c r="D51" t="n">
-        <v>5495</v>
+        <v>86.88</v>
       </c>
       <c r="E51" t="n">
         <v>99.45</v>
@@ -1475,7 +1475,7 @@
         <v>52.99</v>
       </c>
       <c r="D52" t="n">
-        <v>5355</v>
+        <v>93.2</v>
       </c>
       <c r="E52" t="n">
         <v>99.13</v>
@@ -1495,7 +1495,7 @@
         <v>51.83</v>
       </c>
       <c r="D53" t="n">
-        <v>5295</v>
+        <v>91.8</v>
       </c>
       <c r="E53" t="n">
         <v>98.62</v>
@@ -1515,7 +1515,7 @@
         <v>52.47</v>
       </c>
       <c r="D54" t="n">
-        <v>5295</v>
+        <v>91.73</v>
       </c>
       <c r="E54" t="n">
         <v>100.47</v>
@@ -1535,7 +1535,7 @@
         <v>54.11</v>
       </c>
       <c r="D55" t="n">
-        <v>5115</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="E55" t="n">
         <v>99.8</v>
@@ -1555,7 +1555,7 @@
         <v>53.46</v>
       </c>
       <c r="D56" t="n">
-        <v>5115</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="E56" t="n">
         <v>99.76000000000001</v>
@@ -1575,7 +1575,7 @@
         <v>52.48</v>
       </c>
       <c r="D57" t="n">
-        <v>5115</v>
+        <v>86.83</v>
       </c>
       <c r="E57" t="n">
         <v>95.2</v>
@@ -1595,7 +1595,7 @@
         <v>52.1</v>
       </c>
       <c r="D58" t="n">
-        <v>5181</v>
+        <v>88.09</v>
       </c>
       <c r="E58" t="n">
         <v>94.05</v>
@@ -1615,7 +1615,7 @@
         <v>50.52</v>
       </c>
       <c r="D59" t="n">
-        <v>5000.15</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="E59" t="n">
         <v>92.92</v>
@@ -1635,7 +1635,7 @@
         <v>48.93</v>
       </c>
       <c r="D60" t="n">
-        <v>5100.1</v>
+        <v>84.67</v>
       </c>
       <c r="E60" t="n">
         <v>92.62</v>
@@ -1655,7 +1655,7 @@
         <v>48.6</v>
       </c>
       <c r="D61" t="n">
-        <v>5155.05</v>
+        <v>84.81</v>
       </c>
       <c r="E61" t="n">
         <v>92.75</v>
@@ -1675,7 +1675,7 @@
         <v>47.17</v>
       </c>
       <c r="D62" t="n">
-        <v>5233.7</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="E62" t="n">
         <v>92.73999999999999</v>
@@ -1695,7 +1695,7 @@
         <v>45.41</v>
       </c>
       <c r="D63" t="n">
-        <v>5103.5</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="E63" t="n">
         <v>92.95999999999999</v>
@@ -1715,7 +1715,7 @@
         <v>45.19</v>
       </c>
       <c r="D64" t="n">
-        <v>4977.4</v>
+        <v>83.83</v>
       </c>
       <c r="E64" t="n">
         <v>93.93000000000001</v>
@@ -1735,7 +1735,7 @@
         <v>45.41</v>
       </c>
       <c r="D65" t="n">
-        <v>5017.5</v>
+        <v>83.36</v>
       </c>
       <c r="E65" t="n">
         <v>95.2</v>
@@ -1755,7 +1755,7 @@
         <v>44.71</v>
       </c>
       <c r="D66" t="n">
-        <v>5017.5</v>
+        <v>83.45</v>
       </c>
       <c r="E66" t="n">
         <v>95.34999999999999</v>
@@ -1775,7 +1775,7 @@
         <v>44.96</v>
       </c>
       <c r="D67" t="n">
-        <v>5115</v>
+        <v>82.41</v>
       </c>
       <c r="E67" t="n">
         <v>94.98</v>
@@ -1795,7 +1795,7 @@
         <v>45.28</v>
       </c>
       <c r="D68" t="n">
-        <v>5125</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="E68" t="n">
         <v>95.28</v>
@@ -1815,7 +1815,7 @@
         <v>45.54</v>
       </c>
       <c r="D69" t="n">
-        <v>5198.2</v>
+        <v>87.34</v>
       </c>
       <c r="E69" t="n">
         <v>96.55</v>
@@ -1835,7 +1835,7 @@
         <v>45.92</v>
       </c>
       <c r="D70" t="n">
-        <v>5071.33</v>
+        <v>84.69</v>
       </c>
       <c r="E70" t="n">
         <v>96.73</v>
@@ -1855,7 +1855,7 @@
         <v>45.06</v>
       </c>
       <c r="D71" t="n">
-        <v>5023.68</v>
+        <v>83.63</v>
       </c>
       <c r="E71" t="n">
         <v>96.45999999999999</v>
@@ -1875,7 +1875,7 @@
         <v>44.81</v>
       </c>
       <c r="D72" t="n">
-        <v>5100.1</v>
+        <v>83.45</v>
       </c>
       <c r="E72" t="n">
         <v>96.13</v>
@@ -1895,7 +1895,7 @@
         <v>44.77</v>
       </c>
       <c r="D73" t="n">
-        <v>5065.1</v>
+        <v>85.25</v>
       </c>
       <c r="E73" t="n">
         <v>97.47</v>
@@ -1915,7 +1915,7 @@
         <v>44.99</v>
       </c>
       <c r="D74" t="n">
-        <v>5145.25</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="E74" t="n">
         <v>99.01000000000001</v>
@@ -1935,7 +1935,7 @@
         <v>46.92</v>
       </c>
       <c r="D75" t="n">
-        <v>5250</v>
+        <v>85.92</v>
       </c>
       <c r="E75" t="n">
         <v>98.27</v>
@@ -1955,7 +1955,7 @@
         <v>50.39</v>
       </c>
       <c r="D76" t="n">
-        <v>5350</v>
+        <v>86.03</v>
       </c>
       <c r="E76" t="n">
         <v>98.92</v>
@@ -1975,7 +1975,7 @@
         <v>54.16</v>
       </c>
       <c r="D77" t="n">
-        <v>5197.17</v>
+        <v>86.38</v>
       </c>
       <c r="E77" t="n">
         <v>98.09999999999999</v>
@@ -1995,7 +1995,7 @@
         <v>53.04</v>
       </c>
       <c r="D78" t="n">
-        <v>5200</v>
+        <v>87.41</v>
       </c>
       <c r="E78" t="n">
         <v>99.22</v>
@@ -2015,7 +2015,7 @@
         <v>53.01</v>
       </c>
       <c r="D79" t="n">
-        <v>5200</v>
+        <v>87.06</v>
       </c>
       <c r="E79" t="n">
         <v>98.78</v>
@@ -2035,7 +2035,7 @@
         <v>54.14</v>
       </c>
       <c r="D80" t="n">
-        <v>5333.98</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="E80" t="n">
         <v>97.62</v>
@@ -2055,7 +2055,7 @@
         <v>53.55</v>
       </c>
       <c r="D81" t="n">
-        <v>5274.33</v>
+        <v>85.97</v>
       </c>
       <c r="E81" t="n">
         <v>99.31</v>
@@ -2075,7 +2075,7 @@
         <v>53.52</v>
       </c>
       <c r="D82" t="n">
-        <v>5260.01</v>
+        <v>85.14</v>
       </c>
       <c r="E82" t="n">
         <v>98.5</v>
@@ -2095,7 +2095,7 @@
         <v>52.26</v>
       </c>
       <c r="D83" t="n">
-        <v>5285.01</v>
+        <v>86.12</v>
       </c>
       <c r="E83" t="n">
         <v>98.01000000000001</v>
@@ -2115,7 +2115,7 @@
         <v>51.88</v>
       </c>
       <c r="D84" t="n">
-        <v>5681.38</v>
+        <v>85.19</v>
       </c>
       <c r="E84" t="n">
         <v>98.44</v>
@@ -2135,7 +2135,7 @@
         <v>51.31</v>
       </c>
       <c r="D85" t="n">
-        <v>5890</v>
+        <v>86.17</v>
       </c>
       <c r="E85" t="n">
         <v>98.33</v>
@@ -2155,7 +2155,7 @@
         <v>52.4</v>
       </c>
       <c r="D86" t="n">
-        <v>5776.72</v>
+        <v>82.09</v>
       </c>
       <c r="E86" t="n">
         <v>97.95</v>
@@ -2175,7 +2175,7 @@
         <v>50.99</v>
       </c>
       <c r="D87" t="n">
-        <v>5776.72</v>
+        <v>80.25</v>
       </c>
       <c r="E87" t="n">
         <v>95.98999999999999</v>
@@ -2195,7 +2195,7 @@
         <v>50.15</v>
       </c>
       <c r="D88" t="n">
-        <v>5800</v>
+        <v>78.63</v>
       </c>
       <c r="E88" t="n">
         <v>94.79000000000001</v>
@@ -2215,7 +2215,7 @@
         <v>50.61</v>
       </c>
       <c r="D89" t="n">
-        <v>5700</v>
+        <v>78.92</v>
       </c>
       <c r="E89" t="n">
         <v>94.11</v>
@@ -2235,7 +2235,7 @@
         <v>50.99</v>
       </c>
       <c r="D90" t="n">
-        <v>5800</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="E90" t="n">
         <v>94.09</v>
@@ -2255,7 +2255,7 @@
         <v>52.29</v>
       </c>
       <c r="D91" t="n">
-        <v>5800</v>
+        <v>76.81</v>
       </c>
       <c r="E91" t="n">
         <v>93.73</v>
@@ -2275,7 +2275,7 @@
         <v>51.61</v>
       </c>
       <c r="D92" t="n">
-        <v>5799.99</v>
+        <v>79.61</v>
       </c>
       <c r="E92" t="n">
         <v>93.59999999999999</v>
@@ -2295,7 +2295,7 @@
         <v>51.22</v>
       </c>
       <c r="D93" t="n">
-        <v>5950</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="E93" t="n">
         <v>93.06999999999999</v>
@@ -2315,7 +2315,7 @@
         <v>50.97</v>
       </c>
       <c r="D94" t="n">
-        <v>6250</v>
+        <v>76.83</v>
       </c>
       <c r="E94" t="n">
         <v>92.52</v>
@@ -2335,7 +2335,7 @@
         <v>51.05</v>
       </c>
       <c r="D95" t="n">
-        <v>6416.25</v>
+        <v>77.3</v>
       </c>
       <c r="E95" t="n">
         <v>92.97</v>
@@ -2355,7 +2355,7 @@
         <v>50.06</v>
       </c>
       <c r="D96" t="n">
-        <v>6586.67</v>
+        <v>75.98</v>
       </c>
       <c r="E96" t="n">
         <v>91.53</v>
@@ -2375,7 +2375,7 @@
         <v>49.6</v>
       </c>
       <c r="D97" t="n">
-        <v>6500</v>
+        <v>75.12</v>
       </c>
       <c r="E97" t="n">
         <v>91.04000000000001</v>
@@ -2395,7 +2395,7 @@
         <v>49.96</v>
       </c>
       <c r="D98" t="n">
-        <v>6700</v>
+        <v>75.16</v>
       </c>
       <c r="E98" t="n">
         <v>91.37</v>
@@ -2415,7 +2415,7 @@
         <v>49.01</v>
       </c>
       <c r="D99" t="n">
-        <v>6700</v>
+        <v>75.67</v>
       </c>
       <c r="E99" t="n">
         <v>91.05</v>
@@ -2435,7 +2435,7 @@
         <v>48.85</v>
       </c>
       <c r="D100" t="n">
-        <v>6702</v>
+        <v>74.11</v>
       </c>
       <c r="E100" t="n">
         <v>90.01000000000001</v>
@@ -2455,7 +2455,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="n">
-        <v>6560</v>
+        <v>74.61</v>
       </c>
       <c r="E101" t="n">
         <v>89.97</v>
@@ -2475,7 +2475,7 @@
         <v>49.03</v>
       </c>
       <c r="D102" t="n">
-        <v>6890</v>
+        <v>75.78</v>
       </c>
       <c r="E102" t="n">
         <v>90.16</v>
@@ -2495,7 +2495,7 @@
         <v>48.75</v>
       </c>
       <c r="D103" t="n">
-        <v>6890</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="E103" t="n">
         <v>88.91</v>
@@ -2515,7 +2515,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="n">
-        <v>6540</v>
+        <v>75.23</v>
       </c>
       <c r="E104" t="n">
         <v>88</v>
@@ -2535,7 +2535,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="n">
-        <v>6540</v>
+        <v>75.34</v>
       </c>
       <c r="E105" t="n">
         <v>87.44</v>
@@ -2555,7 +2555,7 @@
         <v>49.16</v>
       </c>
       <c r="D106" t="n">
-        <v>6489.98</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="E106" t="n">
         <v>88.59999999999999</v>
@@ -2575,7 +2575,7 @@
         <v>49.91</v>
       </c>
       <c r="D107" t="n">
-        <v>6489.98</v>
+        <v>78.47</v>
       </c>
       <c r="E107" t="n">
         <v>88.51000000000001</v>
@@ -2595,7 +2595,7 @@
         <v>50.88</v>
       </c>
       <c r="D108" t="n">
-        <v>6500</v>
+        <v>78.97</v>
       </c>
       <c r="E108" t="n">
         <v>87.48999999999999</v>
@@ -2615,7 +2615,7 @@
         <v>49.89</v>
       </c>
       <c r="D109" t="n">
-        <v>6600</v>
+        <v>78.62</v>
       </c>
       <c r="E109" t="n">
         <v>86.29000000000001</v>
@@ -2635,7 +2635,7 @@
         <v>49.73</v>
       </c>
       <c r="D110" t="n">
-        <v>6450</v>
+        <v>79.83</v>
       </c>
       <c r="E110" t="n">
         <v>86.09</v>
@@ -2655,7 +2655,7 @@
         <v>49.43</v>
       </c>
       <c r="D111" t="n">
-        <v>6890</v>
+        <v>77.48</v>
       </c>
       <c r="E111" t="n">
         <v>85.01000000000001</v>
@@ -2675,7 +2675,7 @@
         <v>49.21</v>
       </c>
       <c r="D112" t="n">
-        <v>6890</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="E112" t="n">
         <v>86.06999999999999</v>
@@ -2695,7 +2695,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="n">
-        <v>6550</v>
+        <v>77.66</v>
       </c>
       <c r="E113" t="n">
         <v>87.56</v>
@@ -2715,7 +2715,7 @@
         <v>48.86</v>
       </c>
       <c r="D114" t="n">
-        <v>6550</v>
+        <v>76.37</v>
       </c>
       <c r="E114" t="n">
         <v>87.03</v>
@@ -2735,7 +2735,7 @@
         <v>48.75</v>
       </c>
       <c r="D115" t="n">
-        <v>6550</v>
+        <v>76</v>
       </c>
       <c r="E115" t="n">
         <v>85.72</v>
@@ -2755,7 +2755,7 @@
         <v>46.7</v>
       </c>
       <c r="D116" t="n">
-        <v>6550</v>
+        <v>73.69</v>
       </c>
       <c r="E116" t="n">
         <v>82.95999999999999</v>
@@ -2775,7 +2775,7 @@
         <v>45.84</v>
       </c>
       <c r="D117" t="n">
-        <v>6550</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="E117" t="n">
         <v>83.72</v>
@@ -2795,7 +2795,7 @@
         <v>46.33</v>
       </c>
       <c r="D118" t="n">
-        <v>6550</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E118" t="n">
         <v>83.27</v>
@@ -2815,7 +2815,7 @@
         <v>46.75</v>
       </c>
       <c r="D119" t="n">
-        <v>6447.5</v>
+        <v>74.47</v>
       </c>
       <c r="E119" t="n">
         <v>83.33</v>
@@ -2835,7 +2835,7 @@
         <v>46.36</v>
       </c>
       <c r="D120" t="n">
-        <v>6447.5</v>
+        <v>74.44</v>
       </c>
       <c r="E120" t="n">
         <v>82.98999999999999</v>
@@ -2855,7 +2855,7 @@
         <v>49.28</v>
       </c>
       <c r="D121" t="n">
-        <v>6447.5</v>
+        <v>77.28</v>
       </c>
       <c r="E121" t="n">
         <v>86.87</v>
@@ -2875,7 +2875,7 @@
         <v>50.85</v>
       </c>
       <c r="D122" t="n">
-        <v>6447.5</v>
+        <v>78</v>
       </c>
       <c r="E122" t="n">
         <v>86.37</v>
@@ -2895,7 +2895,7 @@
         <v>54.54</v>
       </c>
       <c r="D123" t="n">
-        <v>6600</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="E123" t="n">
         <v>92.84999999999999</v>
@@ -2915,7 +2915,7 @@
         <v>53.4</v>
       </c>
       <c r="D124" t="n">
-        <v>6450</v>
+        <v>85.23</v>
       </c>
       <c r="E124" t="n">
         <v>96.43000000000001</v>
@@ -2935,7 +2935,7 @@
         <v>53.91</v>
       </c>
       <c r="D125" t="n">
-        <v>6450</v>
+        <v>83.89</v>
       </c>
       <c r="E125" t="n">
         <v>97.19</v>
@@ -2955,7 +2955,7 @@
         <v>53.89</v>
       </c>
       <c r="D126" t="n">
-        <v>6450</v>
+        <v>86.14</v>
       </c>
       <c r="E126" t="n">
         <v>98.98999999999999</v>
@@ -2975,7 +2975,7 @@
         <v>55.17</v>
       </c>
       <c r="D127" t="n">
-        <v>6450</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="E127" t="n">
         <v>98.43000000000001</v>
@@ -2995,7 +2995,7 @@
         <v>59.31</v>
       </c>
       <c r="D128" t="n">
-        <v>6675</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="E128" t="n">
         <v>98.5</v>
@@ -3015,7 +3015,7 @@
         <v>60.69</v>
       </c>
       <c r="D129" t="n">
-        <v>6730</v>
+        <v>85.58</v>
       </c>
       <c r="E129" t="n">
         <v>103.6</v>
@@ -3035,7 +3035,7 @@
         <v>60.68</v>
       </c>
       <c r="D130" t="n">
-        <v>6750</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="E130" t="n">
         <v>110.47</v>
@@ -3055,7 +3055,7 @@
         <v>61.3</v>
       </c>
       <c r="D131" t="n">
-        <v>6700</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="E131" t="n">
         <v>109.42</v>
@@ -3075,7 +3075,7 @@
         <v>61.25</v>
       </c>
       <c r="D132" t="n">
-        <v>6700</v>
+        <v>85.3</v>
       </c>
       <c r="E132" t="n">
         <v>111.59</v>
@@ -3095,7 +3095,7 @@
         <v>65.84</v>
       </c>
       <c r="D133" t="n">
-        <v>6700</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="E133" t="n">
         <v>110.65</v>
@@ -3115,7 +3115,7 @@
         <v>67.25</v>
       </c>
       <c r="D134" t="n">
-        <v>6700</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="E134" t="n">
         <v>112.72</v>
@@ -3135,7 +3135,7 @@
         <v>65.62</v>
       </c>
       <c r="D135" t="n">
-        <v>6800</v>
+        <v>84.28</v>
       </c>
       <c r="E135" t="n">
         <v>113.21</v>
@@ -3155,7 +3155,7 @@
         <v>67.61</v>
       </c>
       <c r="D136" t="n">
-        <v>6700</v>
+        <v>85.78</v>
       </c>
       <c r="E136" t="n">
         <v>113.81</v>
@@ -3175,7 +3175,7 @@
         <v>66.55</v>
       </c>
       <c r="D137" t="n">
-        <v>6700</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="E137" t="n">
         <v>118.34</v>
@@ -3195,7 +3195,7 @@
         <v>66.59999999999999</v>
       </c>
       <c r="D138" t="n">
-        <v>6800</v>
+        <v>85.3</v>
       </c>
       <c r="E138" t="n">
         <v>120.67</v>
@@ -3215,7 +3215,7 @@
         <v>67.31</v>
       </c>
       <c r="D139" t="n">
-        <v>6804.55</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="E139" t="n">
         <v>121.17</v>
@@ -3235,7 +3235,7 @@
         <v>66.61</v>
       </c>
       <c r="D140" t="n">
-        <v>6800</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="E140" t="n">
         <v>123.25</v>
@@ -3255,7 +3255,7 @@
         <v>65.81</v>
       </c>
       <c r="D141" t="n">
-        <v>6890</v>
+        <v>91.67</v>
       </c>
       <c r="E141" t="n">
         <v>124.97</v>
@@ -3275,7 +3275,7 @@
         <v>70.06</v>
       </c>
       <c r="D142" t="n">
-        <v>6950</v>
+        <v>98.55</v>
       </c>
       <c r="E142" t="n">
         <v>131.87</v>
@@ -3295,7 +3295,7 @@
         <v>75.31</v>
       </c>
       <c r="D143" t="n">
-        <v>7000</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="E143" t="n">
         <v>131.3</v>
@@ -3315,7 +3315,7 @@
         <v>75.23999999999999</v>
       </c>
       <c r="D144" t="n">
-        <v>7150</v>
+        <v>104.08</v>
       </c>
       <c r="E144" t="n">
         <v>132.31</v>
@@ -3335,7 +3335,7 @@
         <v>72.70999999999999</v>
       </c>
       <c r="D145" t="n">
-        <v>7070</v>
+        <v>104.26</v>
       </c>
       <c r="E145" t="n">
         <v>128.1</v>
@@ -3355,7 +3355,7 @@
         <v>73.68000000000001</v>
       </c>
       <c r="D146" t="n">
-        <v>7099.33</v>
+        <v>107.66</v>
       </c>
       <c r="E146" t="n">
         <v>129.5</v>
@@ -3375,7 +3375,7 @@
         <v>79.20999999999999</v>
       </c>
       <c r="D147" t="n">
-        <v>7070</v>
+        <v>105.57</v>
       </c>
       <c r="E147" t="n">
         <v>134.23</v>
@@ -3395,7 +3395,7 @@
         <v>78.16</v>
       </c>
       <c r="D148" t="n">
-        <v>6999.99</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="E148" t="n">
         <v>132.53</v>
@@ -3415,7 +3415,7 @@
         <v>75.3</v>
       </c>
       <c r="D149" t="n">
-        <v>6999.97</v>
+        <v>104.35</v>
       </c>
       <c r="E149" t="n">
         <v>133.91</v>
@@ -3435,7 +3435,7 @@
         <v>75.59</v>
       </c>
       <c r="D150" t="n">
-        <v>7095.15</v>
+        <v>100.61</v>
       </c>
       <c r="E150" t="n">
         <v>130.71</v>
@@ -3455,7 +3455,7 @@
         <v>75.64</v>
       </c>
       <c r="D151" t="n">
-        <v>7181</v>
+        <v>103.47</v>
       </c>
       <c r="E151" t="n">
         <v>132.37</v>
@@ -3475,7 +3475,7 @@
         <v>76.31999999999999</v>
       </c>
       <c r="D152" t="n">
-        <v>7299</v>
+        <v>101.27</v>
       </c>
       <c r="E152" t="n">
         <v>132.48</v>
@@ -3495,7 +3495,7 @@
         <v>75.54000000000001</v>
       </c>
       <c r="D153" t="n">
-        <v>7300</v>
+        <v>98.28</v>
       </c>
       <c r="E153" t="n">
         <v>132.17</v>
@@ -3515,7 +3515,7 @@
         <v>77.22</v>
       </c>
       <c r="D154" t="n">
-        <v>7300</v>
+        <v>99.52</v>
       </c>
       <c r="E154" t="n">
         <v>130.92</v>
@@ -3535,7 +3535,7 @@
         <v>76.98</v>
       </c>
       <c r="D155" t="n">
-        <v>7400</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="E155" t="n">
         <v>130.03</v>
@@ -3555,7 +3555,7 @@
         <v>76.09</v>
       </c>
       <c r="D156" t="n">
-        <v>7200</v>
+        <v>96.44</v>
       </c>
       <c r="E156" t="n">
         <v>128.75</v>
@@ -3575,7 +3575,7 @@
         <v>73.66</v>
       </c>
       <c r="D157" t="n">
-        <v>7200</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="E157" t="n">
         <v>124.03</v>
@@ -3595,7 +3595,7 @@
         <v>71.55</v>
       </c>
       <c r="D158" t="n">
-        <v>7200</v>
+        <v>100.06</v>
       </c>
       <c r="E158" t="n">
         <v>124.08</v>
@@ -3615,7 +3615,7 @@
         <v>72.05</v>
       </c>
       <c r="D159" t="n">
-        <v>7097.83</v>
+        <v>100.71</v>
       </c>
       <c r="E159" t="n">
         <v>126.07</v>
@@ -3635,7 +3635,7 @@
         <v>69.45</v>
       </c>
       <c r="D160" t="n">
-        <v>7100</v>
+        <v>99.19</v>
       </c>
       <c r="E160" t="n">
         <v>126.95</v>
@@ -3655,7 +3655,7 @@
         <v>69.33</v>
       </c>
       <c r="D161" t="n">
-        <v>7100</v>
+        <v>97.05</v>
       </c>
       <c r="E161" t="n">
         <v>125.69</v>
@@ -3675,7 +3675,7 @@
         <v>66.41</v>
       </c>
       <c r="D162" t="n">
-        <v>7100</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="E162" t="n">
         <v>124.54</v>
@@ -3695,7 +3695,7 @@
         <v>66.93000000000001</v>
       </c>
       <c r="D163" t="n">
-        <v>7099.38</v>
+        <v>94.25</v>
       </c>
       <c r="E163" t="n">
         <v>122.43</v>
@@ -3715,7 +3715,7 @@
         <v>65.54000000000001</v>
       </c>
       <c r="D164" t="n">
-        <v>6911</v>
+        <v>92.95</v>
       </c>
       <c r="E164" t="n">
         <v>116.98</v>
@@ -3735,7 +3735,7 @@
         <v>65.23</v>
       </c>
       <c r="D165" t="n">
-        <v>7000</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="E165" t="n">
         <v>115.79</v>
@@ -3755,7 +3755,7 @@
         <v>68.20999999999999</v>
       </c>
       <c r="D166" t="n">
-        <v>7000</v>
+        <v>95.48</v>
       </c>
       <c r="E166" t="n">
         <v>116.13</v>
@@ -3775,7 +3775,7 @@
         <v>70.69</v>
       </c>
       <c r="D167" t="n">
-        <v>7000</v>
+        <v>93.87</v>
       </c>
       <c r="E167" t="n">
         <v>115.64</v>
@@ -3795,7 +3795,7 @@
         <v>75.98999999999999</v>
       </c>
       <c r="D168" t="n">
-        <v>7000</v>
+        <v>95.03</v>
       </c>
       <c r="E168" t="n">
         <v>115.87</v>
@@ -3815,7 +3815,7 @@
         <v>80.8</v>
       </c>
       <c r="D169" t="n">
-        <v>7000</v>
+        <v>95.02</v>
       </c>
       <c r="E169" t="n">
         <v>117</v>
@@ -3835,7 +3835,7 @@
         <v>77.86</v>
       </c>
       <c r="D170" t="n">
-        <v>7100</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="E170" t="n">
         <v>119.87</v>
@@ -3855,7 +3855,7 @@
         <v>79.41</v>
       </c>
       <c r="D171" t="n">
-        <v>7100</v>
+        <v>96</v>
       </c>
       <c r="E171" t="n">
         <v>120.08</v>
@@ -3875,7 +3875,7 @@
         <v>81.48999999999999</v>
       </c>
       <c r="D172" t="n">
-        <v>7100</v>
+        <v>93.36</v>
       </c>
       <c r="E172" t="n">
         <v>119.02</v>
@@ -3895,7 +3895,7 @@
         <v>80.47</v>
       </c>
       <c r="D173" t="n">
-        <v>7100</v>
+        <v>93.83</v>
       </c>
       <c r="E173" t="n">
         <v>119.49</v>
@@ -3915,7 +3915,7 @@
         <v>79.69</v>
       </c>
       <c r="D174" t="n">
-        <v>7015</v>
+        <v>94.25</v>
       </c>
       <c r="E174" t="n">
         <v>119.07</v>
@@ -3935,7 +3935,7 @@
         <v>79.77</v>
       </c>
       <c r="D175" t="n">
-        <v>7022.5</v>
+        <v>94.67</v>
       </c>
       <c r="E175" t="n">
         <v>117.19</v>
@@ -3955,7 +3955,7 @@
         <v>80.48</v>
       </c>
       <c r="D176" t="n">
-        <v>7000</v>
+        <v>95.17</v>
       </c>
       <c r="E176" t="n">
         <v>116.38</v>
@@ -3975,7 +3975,7 @@
         <v>81.95</v>
       </c>
       <c r="D177" t="n">
-        <v>7100</v>
+        <v>96.08</v>
       </c>
       <c r="E177" t="n">
         <v>116.94</v>
@@ -3995,7 +3995,7 @@
         <v>81.31</v>
       </c>
       <c r="D178" t="n">
-        <v>7093.67</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="E178" t="n">
         <v>116.37</v>
@@ -4015,7 +4015,7 @@
         <v>83.18000000000001</v>
       </c>
       <c r="D179" t="n">
-        <v>7090</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="E179" t="n">
         <v>116.98</v>
@@ -4035,7 +4035,7 @@
         <v>89.42</v>
       </c>
       <c r="D180" t="n">
-        <v>7000</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="E180" t="n">
         <v>117.04</v>
@@ -4055,7 +4055,7 @@
         <v>93.23999999999999</v>
       </c>
       <c r="D181" t="n">
-        <v>7000</v>
+        <v>96.64</v>
       </c>
       <c r="E181" t="n">
         <v>117.01</v>
@@ -4075,7 +4075,7 @@
         <v>90.44</v>
       </c>
       <c r="D182" t="n">
-        <v>7190</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="E182" t="n">
         <v>115.92</v>
@@ -4095,7 +4095,7 @@
         <v>92.79000000000001</v>
       </c>
       <c r="D183" t="n">
-        <v>7142.79</v>
+        <v>97.81</v>
       </c>
       <c r="E183" t="n">
         <v>115.83</v>
@@ -4115,7 +4115,7 @@
         <v>92.70999999999999</v>
       </c>
       <c r="D184" t="n">
-        <v>7100</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="E184" t="n">
         <v>114.61</v>
@@ -4135,7 +4135,7 @@
         <v>92.14</v>
       </c>
       <c r="D185" t="n">
-        <v>7100</v>
+        <v>99.36</v>
       </c>
       <c r="E185" t="n">
         <v>116.63</v>
@@ -4155,7 +4155,7 @@
         <v>91.06</v>
       </c>
       <c r="D186" t="n">
-        <v>7100</v>
+        <v>98.55</v>
       </c>
       <c r="E186" t="n">
         <v>117.29</v>
@@ -4175,7 +4175,7 @@
         <v>92.7</v>
       </c>
       <c r="D187" t="n">
-        <v>7100</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="E187" t="n">
         <v>119.39</v>
@@ -4195,7 +4195,7 @@
         <v>93.06999999999999</v>
       </c>
       <c r="D188" t="n">
-        <v>7100</v>
+        <v>97.37</v>
       </c>
       <c r="E188" t="n">
         <v>120.15</v>
@@ -4215,7 +4215,7 @@
         <v>100.05</v>
       </c>
       <c r="D189" t="n">
-        <v>7100</v>
+        <v>95.89</v>
       </c>
       <c r="E189" t="n">
         <v>120.92</v>
@@ -4235,7 +4235,7 @@
         <v>107.55</v>
       </c>
       <c r="D190" t="n">
-        <v>7100</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="E190" t="n">
         <v>121.24</v>
@@ -4255,7 +4255,7 @@
         <v>105.78</v>
       </c>
       <c r="D191" t="n">
-        <v>7000</v>
+        <v>95.5</v>
       </c>
       <c r="E191" t="n">
         <v>124.78</v>
@@ -4275,7 +4275,7 @@
         <v>113.71</v>
       </c>
       <c r="D192" t="n">
-        <v>7141.11</v>
+        <v>96.84</v>
       </c>
       <c r="E192" t="n">
         <v>125.49</v>
@@ -4295,7 +4295,7 @@
         <v>122.24</v>
       </c>
       <c r="D193" t="n">
-        <v>7141.11</v>
+        <v>97.28</v>
       </c>
       <c r="E193" t="n">
         <v>124.64</v>
@@ -4315,7 +4315,7 @@
         <v>131.41</v>
       </c>
       <c r="D194" t="n">
-        <v>7198</v>
+        <v>98.77</v>
       </c>
       <c r="E194" t="n">
         <v>128.39</v>
@@ -4335,7 +4335,7 @@
         <v>134.03</v>
       </c>
       <c r="D195" t="n">
-        <v>7300</v>
+        <v>98.66</v>
       </c>
       <c r="E195" t="n">
         <v>127.42</v>
@@ -4355,7 +4355,7 @@
         <v>129.94</v>
       </c>
       <c r="D196" t="n">
-        <v>7312.41</v>
+        <v>95.06</v>
       </c>
       <c r="E196" t="n">
         <v>128.32</v>
@@ -4375,7 +4375,7 @@
         <v>126.78</v>
       </c>
       <c r="D197" t="n">
-        <v>7300</v>
+        <v>93.62</v>
       </c>
       <c r="E197" t="n">
         <v>129.68</v>
@@ -4395,7 +4395,7 @@
         <v>136.29</v>
       </c>
       <c r="D198" t="n">
-        <v>7390</v>
+        <v>97.77</v>
       </c>
       <c r="E198" t="n">
         <v>132.65</v>
@@ -4415,7 +4415,7 @@
         <v>146.51</v>
       </c>
       <c r="D199" t="n">
-        <v>7200</v>
+        <v>97.09</v>
       </c>
       <c r="E199" t="n">
         <v>132.95</v>
@@ -4435,7 +4435,7 @@
         <v>145.76</v>
       </c>
       <c r="D200" t="n">
-        <v>7200</v>
+        <v>102.45</v>
       </c>
       <c r="E200" t="n">
         <v>133.58</v>
@@ -4455,7 +4455,7 @@
         <v>141.95</v>
       </c>
       <c r="D201" t="n">
-        <v>7200</v>
+        <v>101.02</v>
       </c>
       <c r="E201" t="n">
         <v>133.34</v>
@@ -4475,7 +4475,7 @@
         <v>152.6</v>
       </c>
       <c r="D202" t="n">
-        <v>7300</v>
+        <v>100.78</v>
       </c>
       <c r="E202" t="n">
         <v>133.61</v>
@@ -4495,7 +4495,7 @@
         <v>155.33</v>
       </c>
       <c r="D203" t="n">
-        <v>7299.99</v>
+        <v>100.18</v>
       </c>
       <c r="E203" t="n">
         <v>136</v>
@@ -4515,7 +4515,7 @@
         <v>152.79</v>
       </c>
       <c r="D204" t="n">
-        <v>7125</v>
+        <v>99.16</v>
       </c>
       <c r="E204" t="n">
         <v>137.57</v>
@@ -4535,7 +4535,7 @@
         <v>163.3</v>
       </c>
       <c r="D205" t="n">
-        <v>7210</v>
+        <v>100.17</v>
       </c>
       <c r="E205" t="n">
         <v>135.83</v>
@@ -4555,7 +4555,7 @@
         <v>163.66</v>
       </c>
       <c r="D206" t="n">
-        <v>7210</v>
+        <v>100.37</v>
       </c>
       <c r="E206" t="n">
         <v>137.43</v>
@@ -4575,7 +4575,7 @@
         <v>171.66</v>
       </c>
       <c r="D207" t="n">
-        <v>7200</v>
+        <v>100.44</v>
       </c>
       <c r="E207" t="n">
         <v>137.01</v>
@@ -4595,7 +4595,7 @@
         <v>184.53</v>
       </c>
       <c r="D208" t="n">
-        <v>7200</v>
+        <v>100.27</v>
       </c>
       <c r="E208" t="n">
         <v>135.15</v>
@@ -4615,7 +4615,7 @@
         <v>192.07</v>
       </c>
       <c r="D209" t="n">
-        <v>7300</v>
+        <v>101.5</v>
       </c>
       <c r="E209" t="n">
         <v>141.6</v>
@@ -4635,7 +4635,7 @@
         <v>178.95</v>
       </c>
       <c r="D210" t="n">
-        <v>7300</v>
+        <v>101.64</v>
       </c>
       <c r="E210" t="n">
         <v>141.84</v>
@@ -4655,7 +4655,7 @@
         <v>165.74</v>
       </c>
       <c r="D211" t="n">
-        <v>7300</v>
+        <v>101.52</v>
       </c>
       <c r="E211" t="n">
         <v>142.7</v>
@@ -4675,7 +4675,7 @@
         <v>174.47</v>
       </c>
       <c r="D212" t="n">
-        <v>7300</v>
+        <v>102.27</v>
       </c>
       <c r="E212" t="n">
         <v>145.7</v>
@@ -4695,7 +4695,7 @@
         <v>173.55</v>
       </c>
       <c r="D213" t="n">
-        <v>7300</v>
+        <v>103.92</v>
       </c>
       <c r="E213" t="n">
         <v>149.62</v>
@@ -4715,7 +4715,7 @@
         <v>169.01</v>
       </c>
       <c r="D214" t="n">
-        <v>7847.5</v>
+        <v>103.54</v>
       </c>
       <c r="E214" t="n">
         <v>147.79</v>
@@ -4735,7 +4735,7 @@
         <v>167.22</v>
       </c>
       <c r="D215" t="n">
-        <v>8400</v>
+        <v>103.57</v>
       </c>
       <c r="E215" t="n">
         <v>145.58</v>
@@ -4755,7 +4755,7 @@
         <v>170.02</v>
       </c>
       <c r="D216" t="n">
-        <v>8400</v>
+        <v>106.76</v>
       </c>
       <c r="E216" t="n">
         <v>145.62</v>
@@ -4775,7 +4775,7 @@
         <v>182.77</v>
       </c>
       <c r="D217" t="n">
-        <v>8800</v>
+        <v>113.84</v>
       </c>
       <c r="E217" t="n">
         <v>145.61</v>
@@ -4795,7 +4795,7 @@
         <v>182.01</v>
       </c>
       <c r="D218" t="n">
-        <v>8600</v>
+        <v>111.32</v>
       </c>
       <c r="E218" t="n">
         <v>144.29</v>
@@ -4815,7 +4815,7 @@
         <v>184.32</v>
       </c>
       <c r="D219" t="n">
-        <v>8500</v>
+        <v>109.83</v>
       </c>
       <c r="E219" t="n">
         <v>145.99</v>
@@ -4835,7 +4835,7 @@
         <v>180.31</v>
       </c>
       <c r="D220" t="n">
-        <v>8500</v>
+        <v>108.33</v>
       </c>
       <c r="E220" t="n">
         <v>146.71</v>
@@ -4855,7 +4855,7 @@
         <v>185.49</v>
       </c>
       <c r="D221" t="n">
-        <v>8550</v>
+        <v>110.67</v>
       </c>
       <c r="E221" t="n">
         <v>153.29</v>
@@ -4875,7 +4875,7 @@
         <v>187.2</v>
       </c>
       <c r="D222" t="n">
-        <v>8500</v>
+        <v>108.02</v>
       </c>
       <c r="E222" t="n">
         <v>162.03</v>
@@ -4895,7 +4895,7 @@
         <v>182.14</v>
       </c>
       <c r="D223" t="n">
-        <v>8567.5</v>
+        <v>107.6</v>
       </c>
       <c r="E223" t="n">
         <v>160.58</v>
@@ -4915,7 +4915,7 @@
         <v>180.81</v>
       </c>
       <c r="D224" t="n">
-        <v>8450</v>
+        <v>108.59</v>
       </c>
       <c r="E224" t="n">
         <v>158.05</v>
@@ -4935,7 +4935,7 @@
         <v>180.36</v>
       </c>
       <c r="D225" t="n">
-        <v>8500</v>
+        <v>108.98</v>
       </c>
       <c r="E225" t="n">
         <v>159.11</v>
@@ -4955,7 +4955,7 @@
         <v>184.59</v>
       </c>
       <c r="D226" t="n">
-        <v>8500</v>
+        <v>108.1</v>
       </c>
       <c r="E226" t="n">
         <v>156.53</v>
@@ -4975,7 +4975,7 @@
         <v>186.44</v>
       </c>
       <c r="D227" t="n">
-        <v>8500</v>
+        <v>108.8</v>
       </c>
       <c r="E227" t="n">
         <v>154.84</v>
@@ -4995,7 +4995,7 @@
         <v>200.42</v>
       </c>
       <c r="D228" t="n">
-        <v>8500</v>
+        <v>110.37</v>
       </c>
       <c r="E228" t="n">
         <v>155.13</v>
@@ -5015,7 +5015,7 @@
         <v>215.45</v>
       </c>
       <c r="D229" t="n">
-        <v>8600.01</v>
+        <v>115.39</v>
       </c>
       <c r="E229" t="n">
         <v>155.35</v>
@@ -5035,7 +5035,7 @@
         <v>212.05</v>
       </c>
       <c r="D230" t="n">
-        <v>8600.01</v>
+        <v>121.62</v>
       </c>
       <c r="E230" t="n">
         <v>160.12</v>
@@ -5055,7 +5055,7 @@
         <v>222.65</v>
       </c>
       <c r="D231" t="n">
-        <v>8700</v>
+        <v>123.1</v>
       </c>
       <c r="E231" t="n">
         <v>166.62</v>
@@ -5075,7 +5075,7 @@
         <v>222.4</v>
       </c>
       <c r="D232" t="n">
-        <v>8699.98</v>
+        <v>121.85</v>
       </c>
       <c r="E232" t="n">
         <v>173.97</v>
@@ -5095,7 +5095,7 @@
         <v>220.89</v>
       </c>
       <c r="D233" t="n">
-        <v>8900</v>
+        <v>125.38</v>
       </c>
       <c r="E233" t="n">
         <v>175.04</v>
@@ -5115,7 +5115,7 @@
         <v>217.2</v>
       </c>
       <c r="D234" t="n">
-        <v>8550</v>
+        <v>125.24</v>
       </c>
       <c r="E234" t="n">
         <v>169.73</v>
@@ -5135,7 +5135,7 @@
         <v>213.43</v>
       </c>
       <c r="D235" t="n">
-        <v>8700</v>
+        <v>125.21</v>
       </c>
       <c r="E235" t="n">
         <v>169.76</v>
@@ -5155,7 +5155,7 @@
         <v>200.25</v>
       </c>
       <c r="D236" t="n">
-        <v>8506</v>
+        <v>122.5</v>
       </c>
       <c r="E236" t="n">
         <v>164.71</v>
@@ -5175,7 +5175,7 @@
         <v>192.27</v>
       </c>
       <c r="D237" t="n">
-        <v>8500</v>
+        <v>124.99</v>
       </c>
       <c r="E237" t="n">
         <v>160.77</v>
@@ -5195,7 +5195,7 @@
         <v>182.32</v>
       </c>
       <c r="D238" t="n">
-        <v>8500</v>
+        <v>126.75</v>
       </c>
       <c r="E238" t="n">
         <v>158.91</v>
@@ -5215,7 +5215,7 @@
         <v>187.39</v>
       </c>
       <c r="D239" t="n">
-        <v>8500</v>
+        <v>124.09</v>
       </c>
       <c r="E239" t="n">
         <v>154.63</v>
@@ -5235,7 +5235,7 @@
         <v>181.9</v>
       </c>
       <c r="D240" t="n">
-        <v>8100</v>
+        <v>117.52</v>
       </c>
       <c r="E240" t="n">
         <v>155.27</v>
@@ -5255,7 +5255,7 @@
         <v>171.93</v>
       </c>
       <c r="D241" t="n">
-        <v>8100</v>
+        <v>114.72</v>
       </c>
       <c r="E241" t="n">
         <v>152.67</v>
@@ -5275,7 +5275,7 @@
         <v>183.8</v>
       </c>
       <c r="D242" t="n">
-        <v>7906</v>
+        <v>116.63</v>
       </c>
       <c r="E242" t="n">
         <v>152.32</v>
@@ -5295,7 +5295,7 @@
         <v>173.92</v>
       </c>
       <c r="D243" t="n">
-        <v>7906</v>
+        <v>113.61</v>
       </c>
       <c r="E243" t="n">
         <v>150.85</v>
@@ -5315,7 +5315,7 @@
         <v>160.96</v>
       </c>
       <c r="D244" t="n">
-        <v>7800</v>
+        <v>105.09</v>
       </c>
       <c r="E244" t="n">
         <v>148.56</v>
@@ -5335,7 +5335,7 @@
         <v>173.03</v>
       </c>
       <c r="D245" t="n">
-        <v>7800</v>
+        <v>107.2</v>
       </c>
       <c r="E245" t="n">
         <v>157.97</v>
@@ -5355,7 +5355,7 @@
         <v>175.37</v>
       </c>
       <c r="D246" t="n">
-        <v>8000</v>
+        <v>110.16</v>
       </c>
       <c r="E246" t="n">
         <v>162.04</v>
@@ -5375,7 +5375,7 @@
         <v>177.86</v>
       </c>
       <c r="D247" t="n">
-        <v>8203</v>
+        <v>112.45</v>
       </c>
       <c r="E247" t="n">
         <v>161.36</v>
@@ -5395,7 +5395,7 @@
         <v>189.74</v>
       </c>
       <c r="D248" t="n">
-        <v>8203</v>
+        <v>120.88</v>
       </c>
       <c r="E248" t="n">
         <v>164.34</v>
@@ -5415,7 +5415,7 @@
         <v>181.59</v>
       </c>
       <c r="D249" t="n">
-        <v>8200</v>
+        <v>122.92</v>
       </c>
       <c r="E249" t="n">
         <v>166.11</v>
@@ -5435,7 +5435,7 @@
         <v>182.02</v>
       </c>
       <c r="D250" t="n">
-        <v>8200</v>
+        <v>127.39</v>
       </c>
       <c r="E250" t="n">
         <v>163.88</v>
@@ -5455,7 +5455,7 @@
         <v>195.67</v>
       </c>
       <c r="D251" t="n">
-        <v>8200</v>
+        <v>125.61</v>
       </c>
       <c r="E251" t="n">
         <v>163.2</v>
@@ -5475,7 +5475,7 @@
         <v>210.35</v>
       </c>
       <c r="D252" t="n">
-        <v>8400</v>
+        <v>125.04</v>
       </c>
       <c r="E252" t="n">
         <v>162.83</v>
@@ -5495,7 +5495,7 @@
         <v>200.66</v>
       </c>
       <c r="D253" t="n">
-        <v>8250</v>
+        <v>123.38</v>
       </c>
       <c r="E253" t="n">
         <v>162.73</v>
@@ -5515,7 +5515,7 @@
         <v>215.71</v>
       </c>
       <c r="D254" t="n">
-        <v>8200</v>
+        <v>122.51</v>
       </c>
       <c r="E254" t="n">
         <v>161.34</v>
@@ -5535,7 +5535,7 @@
         <v>219.02</v>
       </c>
       <c r="D255" t="n">
-        <v>8200</v>
+        <v>122.67</v>
       </c>
       <c r="E255" t="n">
         <v>157.72</v>
@@ -5555,7 +5555,7 @@
         <v>211.07</v>
       </c>
       <c r="D256" t="n">
-        <v>8200</v>
+        <v>127.06</v>
       </c>
       <c r="E256" t="n">
         <v>159.23</v>
@@ -5575,7 +5575,7 @@
         <v>203.49</v>
       </c>
       <c r="D257" t="n">
-        <v>8200</v>
+        <v>127.53</v>
       </c>
       <c r="E257" t="n">
         <v>160.9</v>
@@ -5595,7 +5595,7 @@
         <v>204.42</v>
       </c>
       <c r="D258" t="n">
-        <v>8000</v>
+        <v>130.29</v>
       </c>
       <c r="E258" t="n">
         <v>161.26</v>
@@ -5615,7 +5615,7 @@
         <v>205.27</v>
       </c>
       <c r="D259" t="n">
-        <v>8200</v>
+        <v>126.42</v>
       </c>
       <c r="E259" t="n">
         <v>160.09</v>
@@ -5635,7 +5635,7 @@
         <v>203.88</v>
       </c>
       <c r="D260" t="n">
-        <v>8200</v>
+        <v>126.39</v>
       </c>
       <c r="E260" t="n">
         <v>164.39</v>
@@ -5655,7 +5655,7 @@
         <v>199.91</v>
       </c>
       <c r="D261" t="n">
-        <v>8200</v>
+        <v>124.21</v>
       </c>
       <c r="E261" t="n">
         <v>164.22</v>
@@ -5675,7 +5675,7 @@
         <v>208.7</v>
       </c>
       <c r="D262" t="n">
-        <v>8200</v>
+        <v>124.21</v>
       </c>
       <c r="E262" t="n">
         <v>164.86</v>
@@ -5695,7 +5695,7 @@
         <v>202.16</v>
       </c>
       <c r="D263" t="n">
-        <v>8270</v>
+        <v>133.53</v>
       </c>
       <c r="E263" t="n">
         <v>164.92</v>
@@ -5715,7 +5715,7 @@
         <v>207.62</v>
       </c>
       <c r="D264" t="n">
-        <v>8350</v>
+        <v>136.5</v>
       </c>
       <c r="E264" t="n">
         <v>168.28</v>
@@ -5735,7 +5735,7 @@
         <v>215.49</v>
       </c>
       <c r="D265" t="n">
-        <v>8300</v>
+        <v>145.87</v>
       </c>
       <c r="E265" t="n">
         <v>169.73</v>
@@ -5755,7 +5755,7 @@
         <v>210.86</v>
       </c>
       <c r="D266" t="n">
-        <v>8300</v>
+        <v>135.31</v>
       </c>
       <c r="E266" t="n">
         <v>172.92</v>
@@ -5775,7 +5775,7 @@
         <v>206.13</v>
       </c>
       <c r="D267" t="n">
-        <v>8300</v>
+        <v>141.37</v>
       </c>
       <c r="E267" t="n">
         <v>170.35</v>
@@ -5795,7 +5795,7 @@
         <v>203.83</v>
       </c>
       <c r="D268" t="n">
-        <v>8300</v>
+        <v>137.61</v>
       </c>
       <c r="E268" t="n">
         <v>166.39</v>
@@ -5815,7 +5815,7 @@
         <v>197.71</v>
       </c>
       <c r="D269" t="n">
-        <v>8300</v>
+        <v>134.28</v>
       </c>
       <c r="E269" t="n">
         <v>160.6</v>
@@ -5835,7 +5835,7 @@
         <v>211.19</v>
       </c>
       <c r="D270" t="n">
-        <v>8200</v>
+        <v>135.28</v>
       </c>
       <c r="E270" t="n">
         <v>161.12</v>
@@ -5855,7 +5855,7 @@
         <v>208.72</v>
       </c>
       <c r="D271" t="n">
-        <v>8200</v>
+        <v>144.26</v>
       </c>
       <c r="E271" t="n">
         <v>165.55</v>
@@ -5875,7 +5875,7 @@
         <v>210.24</v>
       </c>
       <c r="D272" t="n">
-        <v>8200</v>
+        <v>147.6</v>
       </c>
       <c r="E272" t="n">
         <v>167.84</v>
@@ -5895,7 +5895,7 @@
         <v>210.85</v>
       </c>
       <c r="D273" t="n">
-        <v>8200</v>
+        <v>155.57</v>
       </c>
       <c r="E273" t="n">
         <v>168.54</v>
@@ -5915,7 +5915,7 @@
         <v>218.19</v>
       </c>
       <c r="D274" t="n">
-        <v>8200</v>
+        <v>150.67</v>
       </c>
       <c r="E274" t="n">
         <v>170.58</v>
@@ -5935,7 +5935,7 @@
         <v>212.29</v>
       </c>
       <c r="D275" t="n">
-        <v>8200</v>
+        <v>145.08</v>
       </c>
       <c r="E275" t="n">
         <v>167.92</v>
@@ -5955,7 +5955,7 @@
         <v>216.76</v>
       </c>
       <c r="D276" t="n">
-        <v>8200</v>
+        <v>134.2</v>
       </c>
       <c r="E276" t="n">
         <v>166.9</v>
@@ -5975,7 +5975,7 @@
         <v>233.02</v>
       </c>
       <c r="D277" t="n">
-        <v>8200</v>
+        <v>124.18</v>
       </c>
       <c r="E277" t="n">
         <v>169.6</v>
@@ -5995,7 +5995,7 @@
         <v>250.5</v>
       </c>
       <c r="D278" t="n">
-        <v>8200</v>
+        <v>122.01</v>
       </c>
       <c r="E278" t="n">
         <v>168.92</v>
@@ -6015,7 +6015,7 @@
         <v>261.76</v>
       </c>
       <c r="D279" t="n">
-        <v>8200</v>
+        <v>114.11</v>
       </c>
       <c r="E279" t="n">
         <v>169.23</v>
@@ -6035,7 +6035,7 @@
         <v>244.28</v>
       </c>
       <c r="D280" t="n">
-        <v>8200</v>
+        <v>107.93</v>
       </c>
       <c r="E280" t="n">
         <v>167.73</v>
@@ -6055,7 +6055,7 @@
         <v>260.85</v>
       </c>
       <c r="D281" t="n">
-        <v>7910.11</v>
+        <v>115.53</v>
       </c>
       <c r="E281" t="n">
         <v>167.71</v>
@@ -6075,7 +6075,7 @@
         <v>266.06</v>
       </c>
       <c r="D282" t="n">
-        <v>7910.11</v>
+        <v>113.01</v>
       </c>
       <c r="E282" t="n">
         <v>165.61</v>
@@ -6095,7 +6095,7 @@
         <v>286.01</v>
       </c>
       <c r="D283" t="n">
-        <v>7910.11</v>
+        <v>117.2</v>
       </c>
       <c r="E283" t="n">
         <v>168.94</v>
@@ -6115,7 +6115,7 @@
         <v>307.46</v>
       </c>
       <c r="D284" t="n">
-        <v>7910.11</v>
+        <v>116.69</v>
       </c>
       <c r="E284" t="n">
         <v>175.4</v>
@@ -6135,7 +6135,7 @@
         <v>328.11</v>
       </c>
       <c r="D285" t="n">
-        <v>7910.11</v>
+        <v>125.21</v>
       </c>
       <c r="E285" t="n">
         <v>181.96</v>
@@ -6155,7 +6155,7 @@
         <v>352.72</v>
       </c>
       <c r="D286" t="n">
-        <v>7580</v>
+        <v>125.01</v>
       </c>
       <c r="E286" t="n">
         <v>184.44</v>
@@ -6175,7 +6175,7 @@
         <v>361.39</v>
       </c>
       <c r="D287" t="n">
-        <v>7780</v>
+        <v>121.07</v>
       </c>
       <c r="E287" t="n">
         <v>184.23</v>
@@ -6195,7 +6195,7 @@
         <v>363.09</v>
       </c>
       <c r="D288" t="n">
-        <v>7780</v>
+        <v>123.17</v>
       </c>
       <c r="E288" t="n">
         <v>184.12</v>
@@ -6215,7 +6215,7 @@
         <v>361.6</v>
       </c>
       <c r="D289" t="n">
-        <v>7780</v>
+        <v>125.12</v>
       </c>
       <c r="E289" t="n">
         <v>187.89</v>
@@ -6235,7 +6235,7 @@
         <v>362.37</v>
       </c>
       <c r="D290" t="n">
-        <v>7870</v>
+        <v>123.33</v>
       </c>
       <c r="E290" t="n">
         <v>195.21</v>
@@ -6255,7 +6255,7 @@
         <v>352.73</v>
       </c>
       <c r="D291" t="n">
-        <v>7870</v>
+        <v>132.17</v>
       </c>
       <c r="E291" t="n">
         <v>193.41</v>
@@ -6275,7 +6275,7 @@
         <v>379.18</v>
       </c>
       <c r="D292" t="n">
-        <v>7677.5</v>
+        <v>127.98</v>
       </c>
       <c r="E292" t="n">
         <v>192.73</v>
@@ -6295,7 +6295,7 @@
         <v>382.91</v>
       </c>
       <c r="D293" t="n">
-        <v>8200</v>
+        <v>128.64</v>
       </c>
       <c r="E293" t="n">
         <v>192.45</v>
@@ -6315,7 +6315,7 @@
         <v>411.63</v>
       </c>
       <c r="D294" t="n">
-        <v>7890</v>
+        <v>131.35</v>
       </c>
       <c r="E294" t="n">
         <v>190.54</v>
@@ -6335,7 +6335,7 @@
         <v>434.41</v>
       </c>
       <c r="D295" t="n">
-        <v>8050</v>
+        <v>129.11</v>
       </c>
       <c r="E295" t="n">
         <v>188.46</v>
@@ -6355,7 +6355,7 @@
         <v>432.86</v>
       </c>
       <c r="D296" t="n">
-        <v>7577.77</v>
+        <v>127.87</v>
       </c>
       <c r="E296" t="n">
         <v>186.97</v>
@@ -6375,7 +6375,7 @@
         <v>401.15</v>
       </c>
       <c r="D297" t="n">
-        <v>7480</v>
+        <v>123.59</v>
       </c>
       <c r="E297" t="n">
         <v>187.04</v>
@@ -6395,7 +6395,7 @@
         <v>371.56</v>
       </c>
       <c r="D298" t="n">
-        <v>7430.88</v>
+        <v>121.54</v>
       </c>
       <c r="E298" t="n">
         <v>186.49</v>
@@ -6415,7 +6415,7 @@
         <v>399.43</v>
       </c>
       <c r="D299" t="n">
-        <v>7500</v>
+        <v>126.8</v>
       </c>
       <c r="E299" t="n">
         <v>190.5</v>
@@ -6435,7 +6435,7 @@
         <v>413.45</v>
       </c>
       <c r="D300" t="n">
-        <v>7500</v>
+        <v>123.69</v>
       </c>
       <c r="E300" t="n">
         <v>192.89</v>
@@ -6455,7 +6455,7 @@
         <v>397.81</v>
       </c>
       <c r="D301" t="n">
-        <v>7500</v>
+        <v>123.33</v>
       </c>
       <c r="E301" t="n">
         <v>196.36</v>
@@ -6475,7 +6475,7 @@
         <v>408.48</v>
       </c>
       <c r="D302" t="n">
-        <v>7420</v>
+        <v>123.07</v>
       </c>
       <c r="E302" t="n">
         <v>201.3</v>
@@ -6495,7 +6495,7 @@
         <v>411.69</v>
       </c>
       <c r="D303" t="n">
-        <v>7510</v>
+        <v>122.11</v>
       </c>
       <c r="E303" t="n">
         <v>203.2</v>
@@ -6515,7 +6515,7 @@
         <v>394.78</v>
       </c>
       <c r="D304" t="n">
-        <v>7510</v>
+        <v>120.16</v>
       </c>
       <c r="E304" t="n">
         <v>196.45</v>
@@ -6535,7 +6535,7 @@
         <v>395.68</v>
       </c>
       <c r="D305" t="n">
-        <v>7200</v>
+        <v>117.99</v>
       </c>
       <c r="E305" t="n">
         <v>197.26</v>
@@ -6555,7 +6555,7 @@
         <v>388.79</v>
       </c>
       <c r="D306" t="n">
-        <v>7400</v>
+        <v>121.41</v>
       </c>
       <c r="E306" t="n">
         <v>199.76</v>
@@ -6575,7 +6575,7 @@
         <v>398.2</v>
       </c>
       <c r="D307" t="n">
-        <v>7400</v>
+        <v>122.39</v>
       </c>
       <c r="E307" t="n">
         <v>206.99</v>
@@ -6595,7 +6595,7 @@
         <v>391.67</v>
       </c>
       <c r="D308" t="n">
-        <v>7635</v>
+        <v>122.67</v>
       </c>
       <c r="E308" t="n">
         <v>210.27</v>
@@ -6615,7 +6615,7 @@
         <v>393.86</v>
       </c>
       <c r="D309" t="n">
-        <v>7600.33</v>
+        <v>122.81</v>
       </c>
       <c r="E309" t="n">
         <v>211.2</v>
@@ -6635,7 +6635,7 @@
         <v>388.31</v>
       </c>
       <c r="D310" t="n">
-        <v>7600.33</v>
+        <v>121.65</v>
       </c>
       <c r="E310" t="n">
         <v>213.62</v>
@@ -6655,7 +6655,7 @@
         <v>415.1</v>
       </c>
       <c r="D311" t="n">
-        <v>7600.33</v>
+        <v>119.77</v>
       </c>
       <c r="E311" t="n">
         <v>214.94</v>
@@ -6675,7 +6675,7 @@
         <v>437.53</v>
       </c>
       <c r="D312" t="n">
-        <v>7600.33</v>
+        <v>119.08</v>
       </c>
       <c r="E312" t="n">
         <v>215.77</v>
@@ -6695,7 +6695,7 @@
         <v>427.69</v>
       </c>
       <c r="D313" t="n">
-        <v>7600.33</v>
+        <v>122.15</v>
       </c>
       <c r="E313" t="n">
         <v>212.54</v>
@@ -6715,7 +6715,7 @@
         <v>436.32</v>
       </c>
       <c r="D314" t="n">
-        <v>7566.89</v>
+        <v>125.3</v>
       </c>
       <c r="E314" t="n">
         <v>217.52</v>
@@ -6735,7 +6735,7 @@
         <v>469.04</v>
       </c>
       <c r="D315" t="n">
-        <v>7566.89</v>
+        <v>128.15</v>
       </c>
       <c r="E315" t="n">
         <v>224.21</v>
@@ -6755,7 +6755,7 @@
         <v>470.27</v>
       </c>
       <c r="D316" t="n">
-        <v>7566.89</v>
+        <v>128.2</v>
       </c>
       <c r="E316" t="n">
         <v>229.82</v>
@@ -6775,7 +6775,7 @@
         <v>493.46</v>
       </c>
       <c r="D317" t="n">
-        <v>7525</v>
+        <v>133.07</v>
       </c>
       <c r="E317" t="n">
         <v>228.96</v>
@@ -6795,7 +6795,7 @@
         <v>489.36</v>
       </c>
       <c r="D318" t="n">
-        <v>7525</v>
+        <v>133.4</v>
       </c>
       <c r="E318" t="n">
         <v>228.15</v>
@@ -6815,7 +6815,7 @@
         <v>487.17</v>
       </c>
       <c r="D319" t="n">
-        <v>7600</v>
+        <v>131.24</v>
       </c>
       <c r="E319" t="n">
         <v>229.59</v>
@@ -6835,7 +6835,7 @@
         <v>516.34</v>
       </c>
       <c r="D320" t="n">
-        <v>7547.5</v>
+        <v>131.58</v>
       </c>
       <c r="E320" t="n">
         <v>219</v>
@@ -6855,7 +6855,7 @@
         <v>555.0700000000001</v>
       </c>
       <c r="D321" t="n">
-        <v>7600</v>
+        <v>133.84</v>
       </c>
       <c r="E321" t="n">
         <v>222.68</v>
@@ -6875,7 +6875,7 @@
         <v>596.7</v>
       </c>
       <c r="D322" t="n">
-        <v>7652.01</v>
+        <v>135.69</v>
       </c>
       <c r="E322" t="n">
         <v>223.49</v>
@@ -6895,7 +6895,7 @@
         <v>626.15</v>
       </c>
       <c r="D323" t="n">
-        <v>7680.36</v>
+        <v>134.19</v>
       </c>
       <c r="E323" t="n">
         <v>218.21</v>
@@ -6915,7 +6915,7 @@
         <v>620.58</v>
       </c>
       <c r="D324" t="n">
-        <v>7706</v>
+        <v>134.36</v>
       </c>
       <c r="E324" t="n">
         <v>215.73</v>
@@ -6935,7 +6935,7 @@
         <v>633.9299999999999</v>
       </c>
       <c r="D325" t="n">
-        <v>7690.87</v>
+        <v>136.49</v>
       </c>
       <c r="E325" t="n">
         <v>217.51</v>
@@ -6955,7 +6955,7 @@
         <v>671.45</v>
       </c>
       <c r="D326" t="n">
-        <v>7822.61</v>
+        <v>137.15</v>
       </c>
       <c r="E326" t="n">
         <v>220.78</v>
@@ -6975,7 +6975,7 @@
         <v>694.78</v>
       </c>
       <c r="D327" t="n">
-        <v>7484.2</v>
+        <v>134.22</v>
       </c>
       <c r="E327" t="n">
         <v>212.45</v>
@@ -6995,7 +6995,7 @@
         <v>698.1799999999999</v>
       </c>
       <c r="D328" t="n">
-        <v>7485</v>
+        <v>133.57</v>
       </c>
       <c r="E328" t="n">
         <v>212.68</v>
@@ -7015,7 +7015,7 @@
         <v>700.45</v>
       </c>
       <c r="D329" t="n">
-        <v>7485</v>
+        <v>132.5</v>
       </c>
       <c r="E329" t="n">
         <v>211.15</v>
@@ -7035,7 +7035,7 @@
         <v>748.55</v>
       </c>
       <c r="D330" t="n">
-        <v>7585.11</v>
+        <v>138.34</v>
       </c>
       <c r="E330" t="n">
         <v>214.43</v>
@@ -7055,7 +7055,7 @@
         <v>767.5700000000001</v>
       </c>
       <c r="D331" t="n">
-        <v>7560</v>
+        <v>136.97</v>
       </c>
       <c r="E331" t="n">
         <v>214.05</v>
@@ -7075,7 +7075,7 @@
         <v>750.26</v>
       </c>
       <c r="D332" t="n">
-        <v>7530</v>
+        <v>134.69</v>
       </c>
       <c r="E332" t="n">
         <v>211.29</v>
@@ -7095,7 +7095,7 @@
         <v>731.1</v>
       </c>
       <c r="D333" t="n">
-        <v>7500</v>
+        <v>133.66</v>
       </c>
       <c r="E333" t="n">
         <v>211.04</v>
@@ -7115,7 +7115,7 @@
         <v>731.1</v>
       </c>
       <c r="D334" t="n">
-        <v>7500</v>
+        <v>133.66</v>
       </c>
       <c r="E334" t="n">
         <v>211.04</v>
@@ -7135,7 +7135,7 @@
         <v>704.95</v>
       </c>
       <c r="D335" t="n">
-        <v>7500</v>
+        <v>133.46</v>
       </c>
       <c r="E335" t="n">
         <v>211.03</v>
@@ -7155,7 +7155,7 @@
         <v>686.84</v>
       </c>
       <c r="D336" t="n">
-        <v>7487.5</v>
+        <v>133.91</v>
       </c>
       <c r="E336" t="n">
         <v>211.32</v>
@@ -7175,7 +7175,7 @@
         <v>688.63</v>
       </c>
       <c r="D337" t="n">
-        <v>7401</v>
+        <v>134.82</v>
       </c>
       <c r="E337" t="n">
         <v>211.05</v>
@@ -7195,7 +7195,7 @@
         <v>694.51</v>
       </c>
       <c r="D338" t="n">
-        <v>7306.58</v>
+        <v>139.41</v>
       </c>
       <c r="E338" t="n">
         <v>217.03</v>
@@ -7215,7 +7215,7 @@
         <v>733.96</v>
       </c>
       <c r="D339" t="n">
-        <v>7380</v>
+        <v>139.32</v>
       </c>
       <c r="E339" t="n">
         <v>221.99</v>
@@ -7235,7 +7235,7 @@
         <v>708.53</v>
       </c>
       <c r="D340" t="n">
-        <v>7280</v>
+        <v>137.98</v>
       </c>
       <c r="E340" t="n">
         <v>224.18</v>
@@ -7255,7 +7255,7 @@
         <v>704.8200000000001</v>
       </c>
       <c r="D341" t="n">
-        <v>7429.82</v>
+        <v>138.09</v>
       </c>
       <c r="E341" t="n">
         <v>223.49</v>
@@ -7275,7 +7275,7 @@
         <v>716.83</v>
       </c>
       <c r="D342" t="n">
-        <v>7417.82</v>
+        <v>136.14</v>
       </c>
       <c r="E342" t="n">
         <v>225.22</v>
@@ -7295,7 +7295,7 @@
         <v>738.22</v>
       </c>
       <c r="D343" t="n">
-        <v>7321.28</v>
+        <v>135.29</v>
       </c>
       <c r="E343" t="n">
         <v>234.65</v>
@@ -7315,7 +7315,7 @@
         <v>712.11</v>
       </c>
       <c r="D344" t="n">
-        <v>7200</v>
+        <v>135.86</v>
       </c>
       <c r="E344" t="n">
         <v>236.18</v>
@@ -7335,7 +7335,7 @@
         <v>717.3200000000001</v>
       </c>
       <c r="D345" t="n">
-        <v>7200</v>
+        <v>139.56</v>
       </c>
       <c r="E345" t="n">
         <v>235.55</v>
@@ -7355,7 +7355,7 @@
         <v>722.41</v>
       </c>
       <c r="D346" t="n">
-        <v>7192.12</v>
+        <v>139.16</v>
       </c>
       <c r="E346" t="n">
         <v>241.07</v>
@@ -7375,7 +7375,7 @@
         <v>716.78</v>
       </c>
       <c r="D347" t="n">
-        <v>7199.99</v>
+        <v>136.98</v>
       </c>
       <c r="E347" t="n">
         <v>241.36</v>
@@ -7395,7 +7395,7 @@
         <v>718.89</v>
       </c>
       <c r="D348" t="n">
-        <v>7159.81</v>
+        <v>132.6</v>
       </c>
       <c r="E348" t="n">
         <v>240.92</v>
@@ -7415,7 +7415,7 @@
         <v>727.91</v>
       </c>
       <c r="D349" t="n">
-        <v>7195.5</v>
+        <v>132.12</v>
       </c>
       <c r="E349" t="n">
         <v>240.94</v>
@@ -7435,7 +7435,7 @@
         <v>786.14</v>
       </c>
       <c r="D350" t="n">
-        <v>7194.55</v>
+        <v>133.47</v>
       </c>
       <c r="E350" t="n">
         <v>246.06</v>
@@ -7455,7 +7455,7 @@
         <v>820.45</v>
       </c>
       <c r="D351" t="n">
-        <v>7349.19</v>
+        <v>132.17</v>
       </c>
       <c r="E351" t="n">
         <v>243.07</v>
@@ -7475,7 +7475,7 @@
         <v>812.26</v>
       </c>
       <c r="D352" t="n">
-        <v>7299.91</v>
+        <v>129.51</v>
       </c>
       <c r="E352" t="n">
         <v>241.02</v>
@@ -7495,7 +7495,7 @@
         <v>840.21</v>
       </c>
       <c r="D353" t="n">
-        <v>7300</v>
+        <v>126.69</v>
       </c>
       <c r="E353" t="n">
         <v>240.96</v>
@@ -7515,7 +7515,7 @@
         <v>787.49</v>
       </c>
       <c r="D354" t="n">
-        <v>7288.24</v>
+        <v>125.14</v>
       </c>
       <c r="E354" t="n">
         <v>239.04</v>
@@ -7535,7 +7535,7 @@
         <v>803.11</v>
       </c>
       <c r="D355" t="n">
-        <v>6995.33</v>
+        <v>123.78</v>
       </c>
       <c r="E355" t="n">
         <v>230.13</v>
@@ -7555,7 +7555,7 @@
         <v>812.22</v>
       </c>
       <c r="D356" t="n">
-        <v>6999.42</v>
+        <v>121.22</v>
       </c>
       <c r="E356" t="n">
         <v>226.79</v>
@@ -7575,7 +7575,7 @@
         <v>782.34</v>
       </c>
       <c r="D357" t="n">
-        <v>6997.99</v>
+        <v>118.82</v>
       </c>
       <c r="E357" t="n">
         <v>222.23</v>
@@ -7595,7 +7595,7 @@
         <v>785.92</v>
       </c>
       <c r="D358" t="n">
-        <v>6995</v>
+        <v>119.12</v>
       </c>
       <c r="E358" t="n">
         <v>223.14</v>
@@ -7615,7 +7615,7 @@
         <v>852.72</v>
       </c>
       <c r="D359" t="n">
-        <v>7008.68</v>
+        <v>129.25</v>
       </c>
       <c r="E359" t="n">
         <v>233</v>
@@ -7635,7 +7635,7 @@
         <v>802.0599999999999</v>
       </c>
       <c r="D360" t="n">
-        <v>7097.92</v>
+        <v>131.21</v>
       </c>
       <c r="E360" t="n">
         <v>242.49</v>
@@ -7655,7 +7655,7 @@
         <v>816.9</v>
       </c>
       <c r="D361" t="n">
-        <v>7098.28</v>
+        <v>134.36</v>
       </c>
       <c r="E361" t="n">
         <v>255.56</v>
@@ -7675,7 +7675,7 @@
         <v>817.51</v>
       </c>
       <c r="D362" t="n">
-        <v>7083.73</v>
+        <v>133.75</v>
       </c>
       <c r="E362" t="n">
         <v>247.35</v>
@@ -7695,7 +7695,7 @@
         <v>810.5599999999999</v>
       </c>
       <c r="D363" t="n">
-        <v>7196</v>
+        <v>131.64</v>
       </c>
       <c r="E363" t="n">
         <v>240.08</v>
@@ -7715,7 +7715,7 @@
         <v>820.34</v>
       </c>
       <c r="D364" t="n">
-        <v>7156.35</v>
+        <v>129.05</v>
       </c>
       <c r="E364" t="n">
         <v>240.23</v>
@@ -7735,7 +7735,7 @@
         <v>838.5700000000001</v>
       </c>
       <c r="D365" t="n">
-        <v>6914</v>
+        <v>135.34</v>
       </c>
       <c r="E365" t="n">
         <v>239.1</v>
@@ -7755,7 +7755,7 @@
         <v>831.63</v>
       </c>
       <c r="D366" t="n">
-        <v>6926.92</v>
+        <v>137.17</v>
       </c>
       <c r="E366" t="n">
         <v>236.82</v>
@@ -7775,7 +7775,7 @@
         <v>832.46</v>
       </c>
       <c r="D367" t="n">
-        <v>7154.17</v>
+        <v>135.37</v>
       </c>
       <c r="E367" t="n">
         <v>239.39</v>
@@ -7795,7 +7795,7 @@
         <v>830.76</v>
       </c>
       <c r="D368" t="n">
-        <v>7000.95</v>
+        <v>135.53</v>
       </c>
       <c r="E368" t="n">
         <v>238.4</v>
@@ -7815,7 +7815,7 @@
         <v>831.5</v>
       </c>
       <c r="D369" t="n">
-        <v>6931</v>
+        <v>135.74</v>
       </c>
       <c r="E369" t="n">
         <v>240.37</v>
@@ -7835,7 +7835,7 @@
         <v>843.22</v>
       </c>
       <c r="D370" t="n">
-        <v>7060.41</v>
+        <v>136.75</v>
       </c>
       <c r="E370" t="n">
         <v>239.96</v>
@@ -7855,7 +7855,7 @@
         <v>849.75</v>
       </c>
       <c r="D371" t="n">
-        <v>7000.39</v>
+        <v>135.27</v>
       </c>
       <c r="E371" t="n">
         <v>242</v>
@@ -7875,7 +7875,7 @@
         <v>914.91</v>
       </c>
       <c r="D372" t="n">
-        <v>7000.07</v>
+        <v>132.95</v>
       </c>
       <c r="E372" t="n">
         <v>240.1</v>
@@ -7895,7 +7895,7 @@
         <v>998.89</v>
       </c>
       <c r="D373" t="n">
-        <v>7055.15</v>
+        <v>133.56</v>
       </c>
       <c r="E373" t="n">
         <v>239.14</v>
@@ -7915,7 +7915,7 @@
         <v>1093.78</v>
       </c>
       <c r="D374" t="n">
-        <v>6999.96</v>
+        <v>134.2</v>
       </c>
       <c r="E374" t="n">
         <v>238.44</v>
@@ -7935,7 +7935,7 @@
         <v>1134.42</v>
       </c>
       <c r="D375" t="n">
-        <v>7039.43</v>
+        <v>133.13</v>
       </c>
       <c r="E375" t="n">
         <v>237.99</v>
@@ -7955,7 +7955,7 @@
         <v>1125.33</v>
       </c>
       <c r="D376" t="n">
-        <v>7047.88</v>
+        <v>132.66</v>
       </c>
       <c r="E376" t="n">
         <v>236.82</v>
@@ -7975,7 +7975,7 @@
         <v>1108.48</v>
       </c>
       <c r="D377" t="n">
-        <v>7045</v>
+        <v>130.83</v>
       </c>
       <c r="E377" t="n">
         <v>237.19</v>
@@ -7995,7 +7995,7 @@
         <v>1130.87</v>
       </c>
       <c r="D378" t="n">
-        <v>7150</v>
+        <v>132.73</v>
       </c>
       <c r="E378" t="n">
         <v>237.17</v>
@@ -8015,7 +8015,7 @@
         <v>1131.23</v>
       </c>
       <c r="D379" t="n">
-        <v>7148.47</v>
+        <v>136.73</v>
       </c>
       <c r="E379" t="n">
         <v>241.07</v>
@@ -8035,7 +8035,7 @@
         <v>1121.9</v>
       </c>
       <c r="D380" t="n">
-        <v>7005</v>
+        <v>134.01</v>
       </c>
       <c r="E380" t="n">
         <v>239.57</v>
@@ -8055,7 +8055,7 @@
         <v>1116.57</v>
       </c>
       <c r="D381" t="n">
-        <v>6998</v>
+        <v>129.74</v>
       </c>
       <c r="E381" t="n">
         <v>235.98</v>
@@ -8075,7 +8075,7 @@
         <v>1117.66</v>
       </c>
       <c r="D382" t="n">
-        <v>6950</v>
+        <v>131.87</v>
       </c>
       <c r="E382" t="n">
         <v>237.86</v>
@@ -8095,7 +8095,7 @@
         <v>1105.05</v>
       </c>
       <c r="D383" t="n">
-        <v>7020</v>
+        <v>131.85</v>
       </c>
       <c r="E383" t="n">
         <v>243</v>
@@ -8115,7 +8115,7 @@
         <v>1081.31</v>
       </c>
       <c r="D384" t="n">
-        <v>6956.96</v>
+        <v>131.3</v>
       </c>
       <c r="E384" t="n">
         <v>239.7</v>
@@ -8135,7 +8135,7 @@
         <v>1043.28</v>
       </c>
       <c r="D385" t="n">
-        <v>6900</v>
+        <v>129.04</v>
       </c>
       <c r="E385" t="n">
         <v>236.59</v>
@@ -8155,7 +8155,7 @@
         <v>1147.61</v>
       </c>
       <c r="D386" t="n">
-        <v>6949.93</v>
+        <v>132.69</v>
       </c>
       <c r="E386" t="n">
         <v>237.68</v>
@@ -8175,7 +8175,7 @@
         <v>1111.93</v>
       </c>
       <c r="D387" t="n">
-        <v>6852.8</v>
+        <v>131.66</v>
       </c>
       <c r="E387" t="n">
         <v>238.1</v>
@@ -8195,7 +8195,7 @@
         <v>1062.97</v>
       </c>
       <c r="D388" t="n">
-        <v>6965.5</v>
+        <v>129.23</v>
       </c>
       <c r="E388" t="n">
         <v>238.31</v>
@@ -8215,7 +8215,7 @@
         <v>1102.44</v>
       </c>
       <c r="D389" t="n">
-        <v>6900</v>
+        <v>128.48</v>
       </c>
       <c r="E389" t="n">
         <v>239.53</v>
@@ -8235,7 +8235,7 @@
         <v>1119.85</v>
       </c>
       <c r="D390" t="n">
-        <v>7029.67</v>
+        <v>130.49</v>
       </c>
       <c r="E390" t="n">
         <v>240.04</v>
@@ -8255,7 +8255,7 @@
         <v>1070.59</v>
       </c>
       <c r="D391" t="n">
-        <v>6848.52</v>
+        <v>129.25</v>
       </c>
       <c r="E391" t="n">
         <v>238.54</v>
@@ -8275,7 +8275,7 @@
         <v>1076.07</v>
       </c>
       <c r="D392" t="n">
-        <v>6997.21</v>
+        <v>129.68</v>
       </c>
       <c r="E392" t="n">
         <v>241.21</v>
@@ -8295,7 +8295,7 @@
         <v>1106.49</v>
       </c>
       <c r="D393" t="n">
-        <v>6911.99</v>
+        <v>129.14</v>
       </c>
       <c r="E393" t="n">
         <v>241.89</v>
@@ -8315,7 +8315,7 @@
         <v>1129.43</v>
       </c>
       <c r="D394" t="n">
-        <v>6925</v>
+        <v>138.55</v>
       </c>
       <c r="E394" t="n">
         <v>241.96</v>
@@ -8335,7 +8335,7 @@
         <v>1169.41</v>
       </c>
       <c r="D395" t="n">
-        <v>6900</v>
+        <v>135.82</v>
       </c>
       <c r="E395" t="n">
         <v>245.48</v>
@@ -8355,7 +8355,7 @@
         <v>1098.83</v>
       </c>
       <c r="D396" t="n">
-        <v>6802</v>
+        <v>133.54</v>
       </c>
       <c r="E396" t="n">
         <v>241.03</v>
@@ -8375,7 +8375,7 @@
         <v>1116.47</v>
       </c>
       <c r="D397" t="n">
-        <v>6847.5</v>
+        <v>133.85</v>
       </c>
       <c r="E397" t="n">
         <v>239.89</v>
@@ -8395,7 +8395,7 @@
         <v>1085.39</v>
       </c>
       <c r="D398" t="n">
-        <v>6800</v>
+        <v>132.26</v>
       </c>
       <c r="E398" t="n">
         <v>241.57</v>
@@ -8415,7 +8415,7 @@
         <v>1028.57</v>
       </c>
       <c r="D399" t="n">
-        <v>6841.79</v>
+        <v>131.32</v>
       </c>
       <c r="E399" t="n">
         <v>248.29</v>
@@ -8435,7 +8435,7 @@
         <v>1026.97</v>
       </c>
       <c r="D400" t="n">
-        <v>6816.66</v>
+        <v>131.83</v>
       </c>
       <c r="E400" t="n">
         <v>241.93</v>
@@ -8455,7 +8455,7 @@
         <v>1007.73</v>
       </c>
       <c r="D401" t="n">
-        <v>6873.43</v>
+        <v>132.85</v>
       </c>
       <c r="E401" t="n">
         <v>242.07</v>
@@ -8475,7 +8475,7 @@
         <v>1037.66</v>
       </c>
       <c r="D402" t="n">
-        <v>6846.32</v>
+        <v>134.07</v>
       </c>
       <c r="E402" t="n">
         <v>241.92</v>
@@ -8495,7 +8495,7 @@
         <v>1021.31</v>
       </c>
       <c r="D403" t="n">
-        <v>6900</v>
+        <v>134.94</v>
       </c>
       <c r="E403" t="n">
         <v>240.05</v>
@@ -8515,7 +8515,7 @@
         <v>1016.95</v>
       </c>
       <c r="D404" t="n">
-        <v>6975</v>
+        <v>135.03</v>
       </c>
       <c r="E404" t="n">
         <v>240.98</v>
@@ -8535,7 +8535,7 @@
         <v>1009.99</v>
       </c>
       <c r="D405" t="n">
-        <v>6887.15</v>
+        <v>134.58</v>
       </c>
       <c r="E405" t="n">
         <v>240.21</v>
@@ -8555,7 +8555,7 @@
         <v>1027.21</v>
       </c>
       <c r="D406" t="n">
-        <v>6863.55</v>
+        <v>133.1</v>
       </c>
       <c r="E406" t="n">
         <v>239.89</v>
@@ -8575,7 +8575,7 @@
         <v>1005.59</v>
       </c>
       <c r="D407" t="n">
-        <v>6817.15</v>
+        <v>132.62</v>
       </c>
       <c r="E407" t="n">
         <v>239.1</v>
@@ -8595,7 +8595,7 @@
         <v>1011.59</v>
       </c>
       <c r="D408" t="n">
-        <v>6894.99</v>
+        <v>132.86</v>
       </c>
       <c r="E408" t="n">
         <v>236.66</v>
@@ -8615,7 +8615,7 @@
         <v>1010.74</v>
       </c>
       <c r="D409" t="n">
-        <v>6900</v>
+        <v>132.9</v>
       </c>
       <c r="E409" t="n">
         <v>235.43</v>
@@ -8635,7 +8635,7 @@
         <v>968.76</v>
       </c>
       <c r="D410" t="n">
-        <v>6860.83</v>
+        <v>133.15</v>
       </c>
       <c r="E410" t="n">
         <v>230.97</v>
@@ -8655,7 +8655,7 @@
         <v>952.62</v>
       </c>
       <c r="D411" t="n">
-        <v>7000</v>
+        <v>134.05</v>
       </c>
       <c r="E411" t="n">
         <v>228.8</v>
@@ -8675,7 +8675,7 @@
         <v>958.51</v>
       </c>
       <c r="D412" t="n">
-        <v>6917.67</v>
+        <v>137.71</v>
       </c>
       <c r="E412" t="n">
         <v>225.44</v>
@@ -8695,7 +8695,7 @@
         <v>1010.23</v>
       </c>
       <c r="D413" t="n">
-        <v>6915</v>
+        <v>137.2</v>
       </c>
       <c r="E413" t="n">
         <v>223.82</v>
@@ -8715,7 +8715,7 @@
         <v>1024.98</v>
       </c>
       <c r="D414" t="n">
-        <v>6997.5</v>
+        <v>136.74</v>
       </c>
       <c r="E414" t="n">
         <v>221.59</v>
@@ -8735,7 +8735,7 @@
         <v>982.41</v>
       </c>
       <c r="D415" t="n">
-        <v>6999.99</v>
+        <v>136.36</v>
       </c>
       <c r="E415" t="n">
         <v>219.64</v>
@@ -8755,7 +8755,7 @@
         <v>973.52</v>
       </c>
       <c r="D416" t="n">
-        <v>6980</v>
+        <v>136.07</v>
       </c>
       <c r="E416" t="n">
         <v>220.84</v>
@@ -8775,7 +8775,7 @@
         <v>971.02</v>
       </c>
       <c r="D417" t="n">
-        <v>6970</v>
+        <v>137.06</v>
       </c>
       <c r="E417" t="n">
         <v>216.61</v>
@@ -8795,7 +8795,7 @@
         <v>972.05</v>
       </c>
       <c r="D418" t="n">
-        <v>6999.5</v>
+        <v>138.52</v>
       </c>
       <c r="E418" t="n">
         <v>216.74</v>
@@ -8815,7 +8815,7 @@
         <v>976.65</v>
       </c>
       <c r="D419" t="n">
-        <v>6984.83</v>
+        <v>142.04</v>
       </c>
       <c r="E419" t="n">
         <v>214.98</v>
@@ -8835,7 +8835,7 @@
         <v>961</v>
       </c>
       <c r="D420" t="n">
-        <v>6980</v>
+        <v>141.03</v>
       </c>
       <c r="E420" t="n">
         <v>212.64</v>
@@ -8855,7 +8855,7 @@
         <v>968.5700000000001</v>
       </c>
       <c r="D421" t="n">
-        <v>6901.61</v>
+        <v>142.27</v>
       </c>
       <c r="E421" t="n">
         <v>217.73</v>
@@ -8875,7 +8875,7 @@
         <v>985.59</v>
       </c>
       <c r="D422" t="n">
-        <v>6962.05</v>
+        <v>145.86</v>
       </c>
       <c r="E422" t="n">
         <v>225.6</v>
@@ -8895,7 +8895,7 @@
         <v>1019.63</v>
       </c>
       <c r="D423" t="n">
-        <v>6962.55</v>
+        <v>141.29</v>
       </c>
       <c r="E423" t="n">
         <v>236.01</v>
@@ -8915,7 +8915,7 @@
         <v>973.75</v>
       </c>
       <c r="D424" t="n">
-        <v>6958.07</v>
+        <v>138.61</v>
       </c>
       <c r="E424" t="n">
         <v>234.02</v>
@@ -8935,7 +8935,7 @@
         <v>998.77</v>
       </c>
       <c r="D425" t="n">
-        <v>6906.02</v>
+        <v>139.78</v>
       </c>
       <c r="E425" t="n">
         <v>232.92</v>
@@ -8955,7 +8955,7 @@
         <v>1021.1</v>
       </c>
       <c r="D426" t="n">
-        <v>6906.02</v>
+        <v>144.28</v>
       </c>
       <c r="E426" t="n">
         <v>234.61</v>
@@ -8975,7 +8975,7 @@
         <v>1000.29</v>
       </c>
       <c r="D427" t="n">
-        <v>6865.56</v>
+        <v>143.56</v>
       </c>
       <c r="E427" t="n">
         <v>233.36</v>
@@ -8995,7 +8995,7 @@
         <v>995.15</v>
       </c>
       <c r="D428" t="n">
-        <v>6888.49</v>
+        <v>143.85</v>
       </c>
       <c r="E428" t="n">
         <v>231.59</v>
@@ -9015,7 +9015,7 @@
         <v>962.59</v>
       </c>
       <c r="D429" t="n">
-        <v>6800</v>
+        <v>143.43</v>
       </c>
       <c r="E429" t="n">
         <v>228.15</v>
@@ -9035,7 +9035,7 @@
         <v>988.84</v>
       </c>
       <c r="D430" t="n">
-        <v>6811.25</v>
+        <v>146.05</v>
       </c>
       <c r="E430" t="n">
         <v>226.92</v>
@@ -9055,7 +9055,7 @@
         <v>968.66</v>
       </c>
       <c r="D431" t="n">
-        <v>6802.27</v>
+        <v>147.76</v>
       </c>
       <c r="E431" t="n">
         <v>228.92</v>
@@ -9075,7 +9075,7 @@
         <v>972.38</v>
       </c>
       <c r="D432" t="n">
-        <v>6802.04</v>
+        <v>149.54</v>
       </c>
       <c r="E432" t="n">
         <v>230.28</v>
@@ -9095,7 +9095,7 @@
         <v>970.4</v>
       </c>
       <c r="D433" t="n">
-        <v>6798.29</v>
+        <v>155.05</v>
       </c>
       <c r="E433" t="n">
         <v>236.5</v>
@@ -9115,7 +9115,7 @@
         <v>978.22</v>
       </c>
       <c r="D434" t="n">
-        <v>6799.9</v>
+        <v>166.92</v>
       </c>
       <c r="E434" t="n">
         <v>239.74</v>
@@ -9135,7 +9135,7 @@
         <v>980.37</v>
       </c>
       <c r="D435" t="n">
-        <v>6865.24</v>
+        <v>172.14</v>
       </c>
       <c r="E435" t="n">
         <v>241.58</v>
@@ -9155,7 +9155,7 @@
         <v>979.28</v>
       </c>
       <c r="D436" t="n">
-        <v>6790</v>
+        <v>169.84</v>
       </c>
       <c r="E436" t="n">
         <v>241.04</v>
@@ -9175,7 +9175,7 @@
         <v>972.25</v>
       </c>
       <c r="D437" t="n">
-        <v>6777.75</v>
+        <v>170.46</v>
       </c>
       <c r="E437" t="n">
         <v>240.95</v>
@@ -9195,7 +9195,7 @@
         <v>960.9299999999999</v>
       </c>
       <c r="D438" t="n">
-        <v>6931.45</v>
+        <v>170</v>
       </c>
       <c r="E438" t="n">
         <v>240.62</v>
@@ -9215,7 +9215,7 @@
         <v>942.12</v>
       </c>
       <c r="D439" t="n">
-        <v>6792</v>
+        <v>167.06</v>
       </c>
       <c r="E439" t="n">
         <v>241.43</v>
@@ -9235,7 +9235,7 @@
         <v>957.41</v>
       </c>
       <c r="D440" t="n">
-        <v>6800</v>
+        <v>170.35</v>
       </c>
       <c r="E440" t="n">
         <v>242.34</v>
@@ -9255,7 +9255,7 @@
         <v>972.66</v>
       </c>
       <c r="D441" t="n">
-        <v>6900</v>
+        <v>169.56</v>
       </c>
       <c r="E441" t="n">
         <v>240.04</v>
@@ -9275,7 +9275,7 @@
         <v>950.21</v>
       </c>
       <c r="D442" t="n">
-        <v>6800</v>
+        <v>168</v>
       </c>
       <c r="E442" t="n">
         <v>240.04</v>
@@ -9295,7 +9295,7 @@
         <v>956.28</v>
       </c>
       <c r="D443" t="n">
-        <v>6797.41</v>
+        <v>165.68</v>
       </c>
       <c r="E443" t="n">
         <v>240.95</v>
@@ -9315,7 +9315,7 @@
         <v>992.48</v>
       </c>
       <c r="D444" t="n">
-        <v>6799.03</v>
+        <v>166.87</v>
       </c>
       <c r="E444" t="n">
         <v>240.86</v>
@@ -9335,7 +9335,7 @@
         <v>1023.34</v>
       </c>
       <c r="D445" t="n">
-        <v>6799.04</v>
+        <v>166.97</v>
       </c>
       <c r="E445" t="n">
         <v>241.19</v>
@@ -9355,7 +9355,7 @@
         <v>1004.29</v>
       </c>
       <c r="D446" t="n">
-        <v>6781.9</v>
+        <v>169.14</v>
       </c>
       <c r="E446" t="n">
         <v>240.96</v>
@@ -9375,7 +9375,7 @@
         <v>1006.59</v>
       </c>
       <c r="D447" t="n">
-        <v>6624.96</v>
+        <v>175.32</v>
       </c>
       <c r="E447" t="n">
         <v>242.03</v>
@@ -9395,7 +9395,7 @@
         <v>986.85</v>
       </c>
       <c r="D448" t="n">
-        <v>6565.12</v>
+        <v>175.6</v>
       </c>
       <c r="E448" t="n">
         <v>245.34</v>
@@ -9415,7 +9415,7 @@
         <v>1014.56</v>
       </c>
       <c r="D449" t="n">
-        <v>6651.3</v>
+        <v>174.48</v>
       </c>
       <c r="E449" t="n">
         <v>247.01</v>
@@ -9435,7 +9435,7 @@
         <v>992.5599999999999</v>
       </c>
       <c r="D450" t="n">
-        <v>6678</v>
+        <v>175.28</v>
       </c>
       <c r="E450" t="n">
         <v>241.33</v>
@@ -9455,7 +9455,7 @@
         <v>1008.04</v>
       </c>
       <c r="D451" t="n">
-        <v>6652.75</v>
+        <v>173.91</v>
       </c>
       <c r="E451" t="n">
         <v>238.98</v>
@@ -9475,7 +9475,7 @@
         <v>1045.14</v>
       </c>
       <c r="D452" t="n">
-        <v>6552.02</v>
+        <v>172.13</v>
       </c>
       <c r="E452" t="n">
         <v>231.88</v>
@@ -9495,7 +9495,7 @@
         <v>1049.6</v>
       </c>
       <c r="D453" t="n">
-        <v>6563.87</v>
+        <v>179.49</v>
       </c>
       <c r="E453" t="n">
         <v>231.53</v>
@@ -9515,7 +9515,7 @@
         <v>1042.34</v>
       </c>
       <c r="D454" t="n">
-        <v>6620</v>
+        <v>180.64</v>
       </c>
       <c r="E454" t="n">
         <v>232.71</v>
@@ -9535,7 +9535,7 @@
         <v>1081.39</v>
       </c>
       <c r="D455" t="n">
-        <v>6600</v>
+        <v>183.31</v>
       </c>
       <c r="E455" t="n">
         <v>231.15</v>
@@ -9555,7 +9555,7 @@
         <v>1120.64</v>
       </c>
       <c r="D456" t="n">
-        <v>6606.01</v>
+        <v>178.54</v>
       </c>
       <c r="E456" t="n">
         <v>232.39</v>
@@ -9575,7 +9575,7 @@
         <v>1125.75</v>
       </c>
       <c r="D457" t="n">
-        <v>6598.09</v>
+        <v>183.22</v>
       </c>
       <c r="E457" t="n">
         <v>230.47</v>
@@ -9595,7 +9595,7 @@
         <v>1116.46</v>
       </c>
       <c r="D458" t="n">
-        <v>6594.33</v>
+        <v>191.41</v>
       </c>
       <c r="E458" t="n">
         <v>228.67</v>
@@ -9615,7 +9615,7 @@
         <v>1091</v>
       </c>
       <c r="D459" t="n">
-        <v>6589.54</v>
+        <v>197.64</v>
       </c>
       <c r="E459" t="n">
         <v>228.09</v>
@@ -9635,7 +9635,7 @@
         <v>1078.28</v>
       </c>
       <c r="D460" t="n">
-        <v>6564.66</v>
+        <v>194.69</v>
       </c>
       <c r="E460" t="n">
         <v>227.4</v>
@@ -9655,7 +9655,7 @@
         <v>1077.85</v>
       </c>
       <c r="D461" t="n">
-        <v>6552.75</v>
+        <v>190.1</v>
       </c>
       <c r="E461" t="n">
         <v>224.52</v>
@@ -9675,7 +9675,7 @@
         <v>1081.79</v>
       </c>
       <c r="D462" t="n">
-        <v>6582</v>
+        <v>194.87</v>
       </c>
       <c r="E462" t="n">
         <v>226.38</v>
@@ -9695,7 +9695,7 @@
         <v>1073.3</v>
       </c>
       <c r="D463" t="n">
-        <v>6600.01</v>
+        <v>194.18</v>
       </c>
       <c r="E463" t="n">
         <v>230.53</v>
@@ -9715,7 +9715,7 @@
         <v>1070.03</v>
       </c>
       <c r="D464" t="n">
-        <v>6558.35</v>
+        <v>194.1</v>
       </c>
       <c r="E464" t="n">
         <v>229.51</v>
@@ -9735,7 +9735,7 @@
         <v>1069.79</v>
       </c>
       <c r="D465" t="n">
-        <v>6600</v>
+        <v>195.47</v>
       </c>
       <c r="E465" t="n">
         <v>230.92</v>
@@ -9755,7 +9755,7 @@
         <v>1056.8</v>
       </c>
       <c r="D466" t="n">
-        <v>6691.17</v>
+        <v>194.94</v>
       </c>
       <c r="E466" t="n">
         <v>232.38</v>
@@ -9775,7 +9775,7 @@
         <v>1058.21</v>
       </c>
       <c r="D467" t="n">
-        <v>6616.31</v>
+        <v>199.66</v>
       </c>
       <c r="E467" t="n">
         <v>235.04</v>
@@ -9795,7 +9795,7 @@
         <v>1054.27</v>
       </c>
       <c r="D468" t="n">
-        <v>6700</v>
+        <v>194.69</v>
       </c>
       <c r="E468" t="n">
         <v>257.44</v>
@@ -9815,7 +9815,7 @@
         <v>1049.87</v>
       </c>
       <c r="D469" t="n">
-        <v>6700</v>
+        <v>192.82</v>
       </c>
       <c r="E469" t="n">
         <v>263.34</v>
@@ -9835,7 +9835,7 @@
         <v>977.45</v>
       </c>
       <c r="D470" t="n">
-        <v>6602</v>
+        <v>179.53</v>
       </c>
       <c r="E470" t="n">
         <v>237.01</v>
@@ -9855,7 +9855,7 @@
         <v>999.46</v>
       </c>
       <c r="D471" t="n">
-        <v>6600.49</v>
+        <v>188.29</v>
       </c>
       <c r="E471" t="n">
         <v>233.45</v>
@@ -9875,7 +9875,7 @@
         <v>999.0599999999999</v>
       </c>
       <c r="D472" t="n">
-        <v>6583.87</v>
+        <v>193.62</v>
       </c>
       <c r="E472" t="n">
         <v>227.44</v>
@@ -9895,7 +9895,7 @@
         <v>1004.49</v>
       </c>
       <c r="D473" t="n">
-        <v>6570.67</v>
+        <v>195.25</v>
       </c>
       <c r="E473" t="n">
         <v>227.38</v>
@@ -9915,7 +9915,7 @@
         <v>1033.78</v>
       </c>
       <c r="D474" t="n">
-        <v>6632.87</v>
+        <v>191.76</v>
       </c>
       <c r="E474" t="n">
         <v>238</v>
@@ -9935,7 +9935,7 @@
         <v>1025.96</v>
       </c>
       <c r="D475" t="n">
-        <v>6681.38</v>
+        <v>191.87</v>
       </c>
       <c r="E475" t="n">
         <v>236.07</v>
@@ -9955,7 +9955,7 @@
         <v>1030.48</v>
       </c>
       <c r="D476" t="n">
-        <v>6701.96</v>
+        <v>192.93</v>
       </c>
       <c r="E476" t="n">
         <v>234.18</v>
@@ -9975,7 +9975,7 @@
         <v>1046.12</v>
       </c>
       <c r="D477" t="n">
-        <v>6711.42</v>
+        <v>197.41</v>
       </c>
       <c r="E477" t="n">
         <v>244.1</v>
@@ -9995,7 +9995,7 @@
         <v>1061.39</v>
       </c>
       <c r="D478" t="n">
-        <v>6715.93</v>
+        <v>194.78</v>
       </c>
       <c r="E478" t="n">
         <v>254.86</v>
@@ -10015,7 +10015,7 @@
         <v>1156.4</v>
       </c>
       <c r="D479" t="n">
-        <v>7387.52</v>
+        <v>197.07</v>
       </c>
       <c r="E479" t="n">
         <v>247.42</v>
@@ -10035,7 +10035,7 @@
         <v>1092.77</v>
       </c>
       <c r="D480" t="n">
-        <v>7330.81</v>
+        <v>193.76</v>
       </c>
       <c r="E480" t="n">
         <v>243.54</v>
@@ -10055,7 +10055,7 @@
         <v>1101.61</v>
       </c>
       <c r="D481" t="n">
-        <v>7155.27</v>
+        <v>204.85</v>
       </c>
       <c r="E481" t="n">
         <v>245.1</v>
@@ -10075,7 +10075,7 @@
         <v>1097.02</v>
       </c>
       <c r="D482" t="n">
-        <v>7355.19</v>
+        <v>213.41</v>
       </c>
       <c r="E482" t="n">
         <v>241.47</v>
@@ -10095,7 +10095,7 @@
         <v>1103.05</v>
       </c>
       <c r="D483" t="n">
-        <v>7423.09</v>
+        <v>222.95</v>
       </c>
       <c r="E483" t="n">
         <v>228.02</v>
@@ -10115,7 +10115,7 @@
         <v>1172.58</v>
       </c>
       <c r="D484" t="n">
-        <v>7586.36</v>
+        <v>233.29</v>
       </c>
       <c r="E484" t="n">
         <v>224.47</v>
@@ -10135,7 +10135,7 @@
         <v>1171.74</v>
       </c>
       <c r="D485" t="n">
-        <v>7511.48</v>
+        <v>222.66</v>
       </c>
       <c r="E485" t="n">
         <v>225.08</v>
@@ -10155,7 +10155,7 @@
         <v>1112.49</v>
       </c>
       <c r="D486" t="n">
-        <v>7429</v>
+        <v>220.76</v>
       </c>
       <c r="E486" t="n">
         <v>214.77</v>
@@ -10175,7 +10175,7 @@
         <v>1074.47</v>
       </c>
       <c r="D487" t="n">
-        <v>7241.37</v>
+        <v>211.17</v>
       </c>
       <c r="E487" t="n">
         <v>211.4</v>
@@ -10195,7 +10195,7 @@
         <v>1081.54</v>
       </c>
       <c r="D488" t="n">
-        <v>7311.65</v>
+        <v>214.67</v>
       </c>
       <c r="E488" t="n">
         <v>218.52</v>
@@ -10215,7 +10215,7 @@
         <v>1119.81</v>
       </c>
       <c r="D489" t="n">
-        <v>7329.35</v>
+        <v>232.59</v>
       </c>
       <c r="E489" t="n">
         <v>220.96</v>
@@ -10235,7 +10235,7 @@
         <v>1119.47</v>
       </c>
       <c r="D490" t="n">
-        <v>7232</v>
+        <v>230.13</v>
       </c>
       <c r="E490" t="n">
         <v>221.74</v>
@@ -10255,7 +10255,7 @@
         <v>1122.54</v>
       </c>
       <c r="D491" t="n">
-        <v>7430.81</v>
+        <v>219.42</v>
       </c>
       <c r="E491" t="n">
         <v>221.01</v>
@@ -10275,7 +10275,7 @@
         <v>1118.35</v>
       </c>
       <c r="D492" t="n">
-        <v>7377.7</v>
+        <v>221.1</v>
       </c>
       <c r="E492" t="n">
         <v>229.82</v>
@@ -10295,7 +10295,7 @@
         <v>1129.99</v>
       </c>
       <c r="D493" t="n">
-        <v>7400</v>
+        <v>225.46</v>
       </c>
       <c r="E493" t="n">
         <v>243.54</v>
@@ -10315,7 +10315,7 @@
         <v>1118.38</v>
       </c>
       <c r="D494" t="n">
-        <v>7450</v>
+        <v>227.26</v>
       </c>
       <c r="E494" t="n">
         <v>241.97</v>
@@ -10335,7 +10335,7 @@
         <v>1131.67</v>
       </c>
       <c r="D495" t="n">
-        <v>7410.78</v>
+        <v>228.61</v>
       </c>
       <c r="E495" t="n">
         <v>245.48</v>
@@ -10355,7 +10355,7 @@
         <v>1102.33</v>
       </c>
       <c r="D496" t="n">
-        <v>7405.48</v>
+        <v>223.26</v>
       </c>
       <c r="E496" t="n">
         <v>247.55</v>
@@ -10375,7 +10375,7 @@
         <v>1100.16</v>
       </c>
       <c r="D497" t="n">
-        <v>7405</v>
+        <v>222.08</v>
       </c>
       <c r="E497" t="n">
         <v>246.17</v>
@@ -10395,7 +10395,7 @@
         <v>1088.21</v>
       </c>
       <c r="D498" t="n">
-        <v>7419.47</v>
+        <v>213.56</v>
       </c>
       <c r="E498" t="n">
         <v>242.06</v>
@@ -10415,7 +10415,7 @@
         <v>1112.82</v>
       </c>
       <c r="D499" t="n">
-        <v>7344.08</v>
+        <v>218.38</v>
       </c>
       <c r="E499" t="n">
         <v>245.8</v>
@@ -10435,7 +10435,7 @@
         <v>1090.27</v>
       </c>
       <c r="D500" t="n">
-        <v>7282.23</v>
+        <v>212.95</v>
       </c>
       <c r="E500" t="n">
         <v>241.47</v>
@@ -10455,7 +10455,7 @@
         <v>1098.54</v>
       </c>
       <c r="D501" t="n">
-        <v>7151.21</v>
+        <v>213.03</v>
       </c>
       <c r="E501" t="n">
         <v>234.99</v>
@@ -10475,7 +10475,7 @@
         <v>1074.62</v>
       </c>
       <c r="D502" t="n">
-        <v>7502.6</v>
+        <v>224.96</v>
       </c>
       <c r="E502" t="n">
         <v>233.31</v>
@@ -10495,7 +10495,7 @@
         <v>1082.22</v>
       </c>
       <c r="D503" t="n">
-        <v>7493.97</v>
+        <v>224.91</v>
       </c>
       <c r="E503" t="n">
         <v>236.59</v>
@@ -10515,7 +10515,7 @@
         <v>1099.13</v>
       </c>
       <c r="D504" t="n">
-        <v>7435.93</v>
+        <v>222.15</v>
       </c>
       <c r="E504" t="n">
         <v>237.4</v>
@@ -10535,7 +10535,7 @@
         <v>1091.23</v>
       </c>
       <c r="D505" t="n">
-        <v>7408.98</v>
+        <v>221.77</v>
       </c>
       <c r="E505" t="n">
         <v>237.46</v>
@@ -10555,7 +10555,7 @@
         <v>1077.85</v>
       </c>
       <c r="D506" t="n">
-        <v>7419.11</v>
+        <v>218.75</v>
       </c>
       <c r="E506" t="n">
         <v>236.36</v>
@@ -10575,7 +10575,7 @@
         <v>1081.74</v>
       </c>
       <c r="D507" t="n">
-        <v>7488.69</v>
+        <v>221.91</v>
       </c>
       <c r="E507" t="n">
         <v>236.93</v>
@@ -10595,7 +10595,7 @@
         <v>1061.72</v>
       </c>
       <c r="D508" t="n">
-        <v>7461.4</v>
+        <v>222.54</v>
       </c>
       <c r="E508" t="n">
         <v>240.68</v>
@@ -10615,7 +10615,7 @@
         <v>1028.34</v>
       </c>
       <c r="D509" t="n">
-        <v>7448.83</v>
+        <v>218.23</v>
       </c>
       <c r="E509" t="n">
         <v>245.97</v>
@@ -10635,7 +10635,7 @@
         <v>994.39</v>
       </c>
       <c r="D510" t="n">
-        <v>7472.25</v>
+        <v>213.99</v>
       </c>
       <c r="E510" t="n">
         <v>243.04</v>
@@ -10655,7 +10655,7 @@
         <v>1005.48</v>
       </c>
       <c r="D511" t="n">
-        <v>7440.24</v>
+        <v>213.91</v>
       </c>
       <c r="E511" t="n">
         <v>242.26</v>
@@ -10675,7 +10675,7 @@
         <v>991.73</v>
       </c>
       <c r="D512" t="n">
-        <v>7424.35</v>
+        <v>212.43</v>
       </c>
       <c r="E512" t="n">
         <v>244.6</v>
@@ -10695,7 +10695,7 @@
         <v>969.36</v>
       </c>
       <c r="D513" t="n">
-        <v>7405.76</v>
+        <v>209.11</v>
       </c>
       <c r="E513" t="n">
         <v>241.94</v>
@@ -10715,7 +10715,7 @@
         <v>959.14</v>
       </c>
       <c r="D514" t="n">
-        <v>7370</v>
+        <v>203.6</v>
       </c>
       <c r="E514" t="n">
         <v>238.89</v>
@@ -10735,7 +10735,7 @@
         <v>952.35</v>
       </c>
       <c r="D515" t="n">
-        <v>7459.6</v>
+        <v>203.24</v>
       </c>
       <c r="E515" t="n">
         <v>236.95</v>
@@ -10755,7 +10755,7 @@
         <v>965.79</v>
       </c>
       <c r="D516" t="n">
-        <v>7431.05</v>
+        <v>206.87</v>
       </c>
       <c r="E516" t="n">
         <v>237.4</v>
@@ -10775,7 +10775,7 @@
         <v>1023.76</v>
       </c>
       <c r="D517" t="n">
-        <v>7433.5</v>
+        <v>206.51</v>
       </c>
       <c r="E517" t="n">
         <v>240.65</v>
@@ -10795,7 +10795,7 @@
         <v>1062.95</v>
       </c>
       <c r="D518" t="n">
-        <v>7395</v>
+        <v>202.69</v>
       </c>
       <c r="E518" t="n">
         <v>243.62</v>
@@ -10815,7 +10815,7 @@
         <v>1140.96</v>
       </c>
       <c r="D519" t="n">
-        <v>7389.25</v>
+        <v>199.88</v>
       </c>
       <c r="E519" t="n">
         <v>240</v>
@@ -10835,7 +10835,7 @@
         <v>1094.36</v>
       </c>
       <c r="D520" t="n">
-        <v>7440.36</v>
+        <v>195.44</v>
       </c>
       <c r="E520" t="n">
         <v>236.13</v>
@@ -10855,7 +10855,7 @@
         <v>1105.68</v>
       </c>
       <c r="D521" t="n">
-        <v>7458.97</v>
+        <v>198.51</v>
       </c>
       <c r="E521" t="n">
         <v>237</v>
@@ -10875,7 +10875,7 @@
         <v>1122.1</v>
       </c>
       <c r="D522" t="n">
-        <v>7455.5</v>
+        <v>200.97</v>
       </c>
       <c r="E522" t="n">
         <v>237.15</v>
@@ -10895,7 +10895,7 @@
         <v>1133.98</v>
       </c>
       <c r="D523" t="n">
-        <v>7444.02</v>
+        <v>208.19</v>
       </c>
       <c r="E523" t="n">
         <v>237.5</v>
@@ -10915,7 +10915,7 @@
         <v>1159.67</v>
       </c>
       <c r="D524" t="n">
-        <v>7430</v>
+        <v>209.1</v>
       </c>
       <c r="E524" t="n">
         <v>237.98</v>
@@ -10935,7 +10935,7 @@
         <v>1172.89</v>
       </c>
       <c r="D525" t="n">
-        <v>7366.5</v>
+        <v>206.43</v>
       </c>
       <c r="E525" t="n">
         <v>239.21</v>
@@ -10955,7 +10955,7 @@
         <v>1144.39</v>
       </c>
       <c r="D526" t="n">
-        <v>7373.39</v>
+        <v>201.86</v>
       </c>
       <c r="E526" t="n">
         <v>236.33</v>
@@ -10975,7 +10975,7 @@
         <v>1090.47</v>
       </c>
       <c r="D527" t="n">
-        <v>7250.3</v>
+        <v>199.44</v>
       </c>
       <c r="E527" t="n">
         <v>234.93</v>
@@ -10995,7 +10995,7 @@
         <v>1100.24</v>
       </c>
       <c r="D528" t="n">
-        <v>7300</v>
+        <v>205.74</v>
       </c>
       <c r="E528" t="n">
         <v>234.61</v>
@@ -11015,7 +11015,7 @@
         <v>1103.6</v>
       </c>
       <c r="D529" t="n">
-        <v>7300</v>
+        <v>204.8</v>
       </c>
       <c r="E529" t="n">
         <v>236.74</v>
@@ -11035,7 +11035,7 @@
         <v>1099.72</v>
       </c>
       <c r="D530" t="n">
-        <v>7297.13</v>
+        <v>204.81</v>
       </c>
       <c r="E530" t="n">
         <v>236.6</v>
@@ -11055,7 +11055,7 @@
         <v>1090.67</v>
       </c>
       <c r="D531" t="n">
-        <v>7345.84</v>
+        <v>202.75</v>
       </c>
       <c r="E531" t="n">
         <v>234.6</v>
@@ -11075,7 +11075,7 @@
         <v>1083.96</v>
       </c>
       <c r="D532" t="n">
-        <v>7300</v>
+        <v>210.37</v>
       </c>
       <c r="E532" t="n">
         <v>240.04</v>
@@ -11095,7 +11095,7 @@
         <v>1099.38</v>
       </c>
       <c r="D533" t="n">
-        <v>7304.8</v>
+        <v>213.33</v>
       </c>
       <c r="E533" t="n">
         <v>238.88</v>
@@ -11115,7 +11115,7 @@
         <v>1096.78</v>
       </c>
       <c r="D534" t="n">
-        <v>7334</v>
+        <v>208.88</v>
       </c>
       <c r="E534" t="n">
         <v>236.63</v>
@@ -11135,7 +11135,7 @@
         <v>1086.93</v>
       </c>
       <c r="D535" t="n">
-        <v>7362.37</v>
+        <v>212.11</v>
       </c>
       <c r="E535" t="n">
         <v>239.01</v>
@@ -11155,7 +11155,7 @@
         <v>1075.7</v>
       </c>
       <c r="D536" t="n">
-        <v>7350.43</v>
+        <v>212.59</v>
       </c>
       <c r="E536" t="n">
         <v>241.9</v>
@@ -11175,7 +11175,7 @@
         <v>1058.16</v>
       </c>
       <c r="D537" t="n">
-        <v>7338.33</v>
+        <v>211.76</v>
       </c>
       <c r="E537" t="n">
         <v>242.94</v>
@@ -11195,7 +11195,7 @@
         <v>1063.5</v>
       </c>
       <c r="D538" t="n">
-        <v>7350</v>
+        <v>213.32</v>
       </c>
       <c r="E538" t="n">
         <v>242.96</v>
@@ -11215,7 +11215,7 @@
         <v>1055</v>
       </c>
       <c r="D539" t="n">
-        <v>7499.2</v>
+        <v>212.91</v>
       </c>
       <c r="E539" t="n">
         <v>243.23</v>
@@ -11235,7 +11235,7 @@
         <v>1055.32</v>
       </c>
       <c r="D540" t="n">
-        <v>7362.02</v>
+        <v>222.58</v>
       </c>
       <c r="E540" t="n">
         <v>240.05</v>
@@ -11255,7 +11255,7 @@
         <v>1064</v>
       </c>
       <c r="D541" t="n">
-        <v>7395.6</v>
+        <v>223.84</v>
       </c>
       <c r="E541" t="n">
         <v>238.84</v>
@@ -11275,7 +11275,7 @@
         <v>1091.36</v>
       </c>
       <c r="D542" t="n">
-        <v>7321.25</v>
+        <v>214.77</v>
       </c>
       <c r="E542" t="n">
         <v>239.07</v>
@@ -11295,7 +11295,7 @@
         <v>1090.78</v>
       </c>
       <c r="D543" t="n">
-        <v>7351</v>
+        <v>218.82</v>
       </c>
       <c r="E543" t="n">
         <v>241.2</v>
@@ -11315,7 +11315,7 @@
         <v>1085.08</v>
       </c>
       <c r="D544" t="n">
-        <v>7350</v>
+        <v>217.24</v>
       </c>
       <c r="E544" t="n">
         <v>240.04</v>
@@ -11335,7 +11335,7 @@
         <v>1087.85</v>
       </c>
       <c r="D545" t="n">
-        <v>7350.05</v>
+        <v>218.28</v>
       </c>
       <c r="E545" t="n">
         <v>241</v>
@@ -11355,7 +11355,7 @@
         <v>1088.8</v>
       </c>
       <c r="D546" t="n">
-        <v>7336.05</v>
+        <v>218.59</v>
       </c>
       <c r="E546" t="n">
         <v>241.79</v>
@@ -11375,7 +11375,7 @@
         <v>1083.51</v>
       </c>
       <c r="D547" t="n">
-        <v>7350</v>
+        <v>221.38</v>
       </c>
       <c r="E547" t="n">
         <v>243.26</v>
@@ -11395,7 +11395,7 @@
         <v>1083.86</v>
       </c>
       <c r="D548" t="n">
-        <v>7467.17</v>
+        <v>223.06</v>
       </c>
       <c r="E548" t="n">
         <v>244.79</v>
@@ -11415,7 +11415,7 @@
         <v>1108.27</v>
       </c>
       <c r="D549" t="n">
-        <v>7402.33</v>
+        <v>225.48</v>
       </c>
       <c r="E549" t="n">
         <v>247.5</v>
@@ -11435,7 +11435,7 @@
         <v>1106.57</v>
       </c>
       <c r="D550" t="n">
-        <v>7383.92</v>
+        <v>226.81</v>
       </c>
       <c r="E550" t="n">
         <v>241.03</v>
@@ -11455,7 +11455,7 @@
         <v>1096</v>
       </c>
       <c r="D551" t="n">
-        <v>7398.55</v>
+        <v>227.35</v>
       </c>
       <c r="E551" t="n">
         <v>239.85</v>
@@ -11475,7 +11475,7 @@
         <v>1075.89</v>
       </c>
       <c r="D552" t="n">
-        <v>7374.94</v>
+        <v>218.17</v>
       </c>
       <c r="E552" t="n">
         <v>235.48</v>
@@ -11495,7 +11495,7 @@
         <v>1077.06</v>
       </c>
       <c r="D553" t="n">
-        <v>7374.98</v>
+        <v>224.19</v>
       </c>
       <c r="E553" t="n">
         <v>239.12</v>
@@ -11515,7 +11515,7 @@
         <v>1087.68</v>
       </c>
       <c r="D554" t="n">
-        <v>7385.78</v>
+        <v>232.75</v>
       </c>
       <c r="E554" t="n">
         <v>244.9</v>
@@ -11535,7 +11535,7 @@
         <v>1076.62</v>
       </c>
       <c r="D555" t="n">
-        <v>7371.5</v>
+        <v>232.73</v>
       </c>
       <c r="E555" t="n">
         <v>247.4</v>
@@ -11555,7 +11555,7 @@
         <v>1092.54</v>
       </c>
       <c r="D556" t="n">
-        <v>7398</v>
+        <v>234.68</v>
       </c>
       <c r="E556" t="n">
         <v>256.46</v>
@@ -11575,7 +11575,7 @@
         <v>1086.63</v>
       </c>
       <c r="D557" t="n">
-        <v>7350</v>
+        <v>226.77</v>
       </c>
       <c r="E557" t="n">
         <v>265.33</v>
@@ -11595,7 +11595,7 @@
         <v>1044.54</v>
       </c>
       <c r="D558" t="n">
-        <v>7200.02</v>
+        <v>213.07</v>
       </c>
       <c r="E558" t="n">
         <v>256.88</v>
@@ -11615,7 +11615,7 @@
         <v>1086.01</v>
       </c>
       <c r="D559" t="n">
-        <v>7242.95</v>
+        <v>214.89</v>
       </c>
       <c r="E559" t="n">
         <v>260.64</v>
@@ -11635,7 +11635,7 @@
         <v>1100.79</v>
       </c>
       <c r="D560" t="n">
-        <v>7206.35</v>
+        <v>208.52</v>
       </c>
       <c r="E560" t="n">
         <v>259.87</v>
@@ -11655,7 +11655,7 @@
         <v>1149.88</v>
       </c>
       <c r="D561" t="n">
-        <v>7183.48</v>
+        <v>214.75</v>
       </c>
       <c r="E561" t="n">
         <v>257.06</v>
@@ -11675,7 +11675,7 @@
         <v>1143</v>
       </c>
       <c r="D562" t="n">
-        <v>7070.85</v>
+        <v>212.16</v>
       </c>
       <c r="E562" t="n">
         <v>255.9</v>
@@ -11695,7 +11695,7 @@
         <v>1186.58</v>
       </c>
       <c r="D563" t="n">
-        <v>7173.33</v>
+        <v>212.02</v>
       </c>
       <c r="E563" t="n">
         <v>258.14</v>
@@ -11715,7 +11715,7 @@
         <v>1191.8</v>
       </c>
       <c r="D564" t="n">
-        <v>7114.77</v>
+        <v>214.32</v>
       </c>
       <c r="E564" t="n">
         <v>256.02</v>
@@ -11735,7 +11735,7 @@
         <v>1169.78</v>
       </c>
       <c r="D565" t="n">
-        <v>7100</v>
+        <v>211.7</v>
       </c>
       <c r="E565" t="n">
         <v>253.09</v>
@@ -11755,7 +11755,7 @@
         <v>1232.22</v>
       </c>
       <c r="D566" t="n">
-        <v>7071.73</v>
+        <v>214.08</v>
       </c>
       <c r="E566" t="n">
         <v>252.92</v>
@@ -11775,7 +11775,7 @@
         <v>1316.34</v>
       </c>
       <c r="D567" t="n">
-        <v>7100</v>
+        <v>212.88</v>
       </c>
       <c r="E567" t="n">
         <v>255.65</v>
@@ -11795,7 +11795,7 @@
         <v>1352.27</v>
       </c>
       <c r="D568" t="n">
-        <v>7001.14</v>
+        <v>212.23</v>
       </c>
       <c r="E568" t="n">
         <v>279</v>
@@ -11815,7 +11815,7 @@
         <v>1370.41</v>
       </c>
       <c r="D569" t="n">
-        <v>7054.21</v>
+        <v>213.28</v>
       </c>
       <c r="E569" t="n">
         <v>269.9</v>
@@ -11835,7 +11835,7 @@
         <v>1329.9</v>
       </c>
       <c r="D570" t="n">
-        <v>7048.99</v>
+        <v>214.36</v>
       </c>
       <c r="E570" t="n">
         <v>269.2</v>
@@ -11855,7 +11855,7 @@
         <v>1304.23</v>
       </c>
       <c r="D571" t="n">
-        <v>6998</v>
+        <v>211.69</v>
       </c>
       <c r="E571" t="n">
         <v>265.2</v>
@@ -11875,7 +11875,7 @@
         <v>1359.99</v>
       </c>
       <c r="D572" t="n">
-        <v>6994.34</v>
+        <v>212.37</v>
       </c>
       <c r="E572" t="n">
         <v>271.61</v>
@@ -11895,7 +11895,7 @@
         <v>1309.74</v>
       </c>
       <c r="D573" t="n">
-        <v>6990.17</v>
+        <v>208</v>
       </c>
       <c r="E573" t="n">
         <v>277.27</v>
@@ -11915,7 +11915,7 @@
         <v>1316.33</v>
       </c>
       <c r="D574" t="n">
-        <v>6887</v>
+        <v>207.81</v>
       </c>
       <c r="E574" t="n">
         <v>271.96</v>
@@ -11935,7 +11935,7 @@
         <v>1263.81</v>
       </c>
       <c r="D575" t="n">
-        <v>6804.04</v>
+        <v>200.38</v>
       </c>
       <c r="E575" t="n">
         <v>264.21</v>
@@ -11955,7 +11955,7 @@
         <v>1297.6</v>
       </c>
       <c r="D576" t="n">
-        <v>6902.27</v>
+        <v>203.25</v>
       </c>
       <c r="E576" t="n">
         <v>273.24</v>
@@ -11975,7 +11975,7 @@
         <v>1343.15</v>
       </c>
       <c r="D577" t="n">
-        <v>7190.36</v>
+        <v>200.22</v>
       </c>
       <c r="E577" t="n">
         <v>272.03</v>
@@ -11995,7 +11995,7 @@
         <v>1321.74</v>
       </c>
       <c r="D578" t="n">
-        <v>7018</v>
+        <v>202.93</v>
       </c>
       <c r="E578" t="n">
         <v>269.35</v>
@@ -12015,7 +12015,7 @@
         <v>1246.94</v>
       </c>
       <c r="D579" t="n">
-        <v>7132.19</v>
+        <v>196.63</v>
       </c>
       <c r="E579" t="n">
         <v>262.89</v>
@@ -12035,7 +12035,7 @@
         <v>1122.28</v>
       </c>
       <c r="D580" t="n">
-        <v>6998.84</v>
+        <v>179.39</v>
       </c>
       <c r="E580" t="n">
         <v>253.07</v>
@@ -12055,7 +12055,7 @@
         <v>1206.54</v>
       </c>
       <c r="D581" t="n">
-        <v>7119.15</v>
+        <v>184.55</v>
       </c>
       <c r="E581" t="n">
         <v>256.24</v>
@@ -12075,7 +12075,7 @@
         <v>1315.47</v>
       </c>
       <c r="D582" t="n">
-        <v>7164.67</v>
+        <v>203.01</v>
       </c>
       <c r="E582" t="n">
         <v>281.84</v>
@@ -12095,7 +12095,7 @@
         <v>1318.54</v>
       </c>
       <c r="D583" t="n">
-        <v>7074.09</v>
+        <v>218.66</v>
       </c>
       <c r="E583" t="n">
         <v>275.92</v>
@@ -12115,7 +12115,7 @@
         <v>1314.29</v>
       </c>
       <c r="D584" t="n">
-        <v>7073.09</v>
+        <v>212.67</v>
       </c>
       <c r="E584" t="n">
         <v>280.24</v>
@@ -12135,7 +12135,7 @@
         <v>1315.57</v>
       </c>
       <c r="D585" t="n">
-        <v>7180</v>
+        <v>213.73</v>
       </c>
       <c r="E585" t="n">
         <v>285.6</v>
@@ -12155,7 +12155,7 @@
         <v>1299.82</v>
       </c>
       <c r="D586" t="n">
-        <v>7091.78</v>
+        <v>211.5</v>
       </c>
       <c r="E586" t="n">
         <v>286.62</v>
@@ -12175,7 +12175,7 @@
         <v>1300.15</v>
       </c>
       <c r="D587" t="n">
-        <v>7068.64</v>
+        <v>211.7</v>
       </c>
       <c r="E587" t="n">
         <v>286.01</v>
@@ -12195,7 +12195,7 @@
         <v>1285.69</v>
       </c>
       <c r="D588" t="n">
-        <v>7050.1</v>
+        <v>209.7</v>
       </c>
       <c r="E588" t="n">
         <v>287.46</v>
@@ -12215,7 +12215,7 @@
         <v>1275.03</v>
       </c>
       <c r="D589" t="n">
-        <v>7070.05</v>
+        <v>213.74</v>
       </c>
       <c r="E589" t="n">
         <v>288.89</v>
@@ -12235,7 +12235,7 @@
         <v>1263.86</v>
       </c>
       <c r="D590" t="n">
-        <v>7054.42</v>
+        <v>211.9</v>
       </c>
       <c r="E590" t="n">
         <v>286.28</v>
@@ -12255,7 +12255,7 @@
         <v>1252.46</v>
       </c>
       <c r="D591" t="n">
-        <v>7018.72</v>
+        <v>212.37</v>
       </c>
       <c r="E591" t="n">
         <v>287.93</v>
@@ -12275,7 +12275,7 @@
         <v>1216.17</v>
       </c>
       <c r="D592" t="n">
-        <v>7013.36</v>
+        <v>208.95</v>
       </c>
       <c r="E592" t="n">
         <v>284.69</v>
@@ -12295,7 +12295,7 @@
         <v>1203.28</v>
       </c>
       <c r="D593" t="n">
-        <v>7010</v>
+        <v>209.41</v>
       </c>
       <c r="E593" t="n">
         <v>289.28</v>
@@ -12315,7 +12315,7 @@
         <v>1199.3</v>
       </c>
       <c r="D594" t="n">
-        <v>7025.4</v>
+        <v>209.17</v>
       </c>
       <c r="E594" t="n">
         <v>290.51</v>
@@ -12335,7 +12335,7 @@
         <v>1185.86</v>
       </c>
       <c r="D595" t="n">
-        <v>7001.11</v>
+        <v>209.49</v>
       </c>
       <c r="E595" t="n">
         <v>303.29</v>
@@ -12355,7 +12355,7 @@
         <v>1171.79</v>
       </c>
       <c r="D596" t="n">
-        <v>7041.26</v>
+        <v>207.98</v>
       </c>
       <c r="E596" t="n">
         <v>305.48</v>
@@ -12375,7 +12375,7 @@
         <v>1180.26</v>
       </c>
       <c r="D597" t="n">
-        <v>7085.73</v>
+        <v>209.15</v>
       </c>
       <c r="E597" t="n">
         <v>309.42</v>
@@ -12395,7 +12395,7 @@
         <v>1162.12</v>
       </c>
       <c r="D598" t="n">
-        <v>7036.18</v>
+        <v>211.89</v>
       </c>
       <c r="E598" t="n">
         <v>310.48</v>
@@ -12415,7 +12415,7 @@
         <v>1148.47</v>
       </c>
       <c r="D599" t="n">
-        <v>7088.61</v>
+        <v>209.95</v>
       </c>
       <c r="E599" t="n">
         <v>303.94</v>
@@ -12435,7 +12435,7 @@
         <v>1145.05</v>
       </c>
       <c r="D600" t="n">
-        <v>7000</v>
+        <v>210.32</v>
       </c>
       <c r="E600" t="n">
         <v>309.36</v>
@@ -12455,7 +12455,7 @@
         <v>1197.93</v>
       </c>
       <c r="D601" t="n">
-        <v>7000.01</v>
+        <v>215.31</v>
       </c>
       <c r="E601" t="n">
         <v>310.86</v>
@@ -12475,7 +12475,7 @@
         <v>1163.12</v>
       </c>
       <c r="D602" t="n">
-        <v>7014.48</v>
+        <v>212.05</v>
       </c>
       <c r="E602" t="n">
         <v>310.99</v>
@@ -12495,7 +12495,7 @@
         <v>1138.52</v>
       </c>
       <c r="D603" t="n">
-        <v>7007.69</v>
+        <v>208.86</v>
       </c>
       <c r="E603" t="n">
         <v>306.33</v>
@@ -12515,7 +12515,7 @@
         <v>1138.28</v>
       </c>
       <c r="D604" t="n">
-        <v>7007.48</v>
+        <v>213.05</v>
       </c>
       <c r="E604" t="n">
         <v>308.45</v>
@@ -12535,7 +12535,7 @@
         <v>1131.51</v>
       </c>
       <c r="D605" t="n">
-        <v>7010</v>
+        <v>214.26</v>
       </c>
       <c r="E605" t="n">
         <v>307.06</v>
@@ -12555,7 +12555,7 @@
         <v>1125.26</v>
       </c>
       <c r="D606" t="n">
-        <v>7009.84</v>
+        <v>211.17</v>
       </c>
       <c r="E606" t="n">
         <v>309.18</v>
@@ -12575,7 +12575,7 @@
         <v>1118.29</v>
       </c>
       <c r="D607" t="n">
-        <v>7004.77</v>
+        <v>210.68</v>
       </c>
       <c r="E607" t="n">
         <v>308.08</v>
@@ -12595,7 +12595,7 @@
         <v>1117.48</v>
       </c>
       <c r="D608" t="n">
-        <v>6999.99</v>
+        <v>212.25</v>
       </c>
       <c r="E608" t="n">
         <v>308.25</v>
@@ -12615,7 +12615,7 @@
         <v>1065.51</v>
       </c>
       <c r="D609" t="n">
-        <v>7007.87</v>
+        <v>203.86</v>
       </c>
       <c r="E609" t="n">
         <v>304.76</v>
@@ -12635,7 +12635,7 @@
         <v>1131.35</v>
       </c>
       <c r="D610" t="n">
-        <v>7036.4</v>
+        <v>218.01</v>
       </c>
       <c r="E610" t="n">
         <v>320.49</v>
@@ -12655,7 +12655,7 @@
         <v>1094.77</v>
       </c>
       <c r="D611" t="n">
-        <v>7047.5</v>
+        <v>217.85</v>
       </c>
       <c r="E611" t="n">
         <v>320.2</v>
@@ -12675,7 +12675,7 @@
         <v>1094.57</v>
       </c>
       <c r="D612" t="n">
-        <v>6976.85</v>
+        <v>217.29</v>
       </c>
       <c r="E612" t="n">
         <v>319.76</v>
@@ -12695,7 +12695,7 @@
         <v>1137.78</v>
       </c>
       <c r="D613" t="n">
-        <v>7031.4</v>
+        <v>221.19</v>
       </c>
       <c r="E613" t="n">
         <v>329.28</v>
@@ -12715,7 +12715,7 @@
         <v>1139.82</v>
       </c>
       <c r="D614" t="n">
-        <v>7046</v>
+        <v>220.56</v>
       </c>
       <c r="E614" t="n">
         <v>332.05</v>
@@ -12735,7 +12735,7 @@
         <v>1130.7</v>
       </c>
       <c r="D615" t="n">
-        <v>7015</v>
+        <v>221.57</v>
       </c>
       <c r="E615" t="n">
         <v>345.36</v>
@@ -12755,7 +12755,7 @@
         <v>1140.07</v>
       </c>
       <c r="D616" t="n">
-        <v>7040.11</v>
+        <v>222.92</v>
       </c>
       <c r="E616" t="n">
         <v>357.12</v>
@@ -12775,7 +12775,7 @@
         <v>1163.45</v>
       </c>
       <c r="D617" t="n">
-        <v>7000.92</v>
+        <v>229.09</v>
       </c>
       <c r="E617" t="n">
         <v>351.42</v>
@@ -12795,7 +12795,7 @@
         <v>1192.32</v>
       </c>
       <c r="D618" t="n">
-        <v>7038.09</v>
+        <v>227.28</v>
       </c>
       <c r="E618" t="n">
         <v>355.6</v>
@@ -12815,7 +12815,7 @@
         <v>1204.61</v>
       </c>
       <c r="D619" t="n">
-        <v>7086.5</v>
+        <v>229.14</v>
       </c>
       <c r="E619" t="n">
         <v>358.98</v>
@@ -12835,7 +12835,7 @@
         <v>1198.89</v>
       </c>
       <c r="D620" t="n">
-        <v>7224.92</v>
+        <v>229.24</v>
       </c>
       <c r="E620" t="n">
         <v>362.4</v>
@@ -12855,7 +12855,7 @@
         <v>1194.98</v>
       </c>
       <c r="D621" t="n">
-        <v>7181</v>
+        <v>228.02</v>
       </c>
       <c r="E621" t="n">
         <v>363.27</v>
@@ -12875,7 +12875,7 @@
         <v>1221.65</v>
       </c>
       <c r="D622" t="n">
-        <v>7160.54</v>
+        <v>226.62</v>
       </c>
       <c r="E622" t="n">
         <v>374.79</v>
@@ -12895,7 +12895,7 @@
         <v>1227.11</v>
       </c>
       <c r="D623" t="n">
-        <v>7150.5</v>
+        <v>227.89</v>
       </c>
       <c r="E623" t="n">
         <v>375.42</v>
@@ -12915,7 +12915,7 @@
         <v>1278.65</v>
       </c>
       <c r="D624" t="n">
-        <v>7145.61</v>
+        <v>227.11</v>
       </c>
       <c r="E624" t="n">
         <v>375.82</v>
@@ -12935,7 +12935,7 @@
         <v>1301.71</v>
       </c>
       <c r="D625" t="n">
-        <v>7199</v>
+        <v>224.43</v>
       </c>
       <c r="E625" t="n">
         <v>365.97</v>
@@ -12955,7 +12955,7 @@
         <v>1293.27</v>
       </c>
       <c r="D626" t="n">
-        <v>7244.89</v>
+        <v>224.37</v>
       </c>
       <c r="E626" t="n">
         <v>356.83</v>
@@ -12975,7 +12975,7 @@
         <v>1293.29</v>
       </c>
       <c r="D627" t="n">
-        <v>7235</v>
+        <v>225.18</v>
       </c>
       <c r="E627" t="n">
         <v>360.92</v>
@@ -12995,7 +12995,7 @@
         <v>1270.82</v>
       </c>
       <c r="D628" t="n">
-        <v>7313.03</v>
+        <v>223.28</v>
       </c>
       <c r="E628" t="n">
         <v>355.88</v>
@@ -13015,7 +13015,7 @@
         <v>1262.92</v>
       </c>
       <c r="D629" t="n">
-        <v>7400</v>
+        <v>221.18</v>
       </c>
       <c r="E629" t="n">
         <v>355.66</v>
@@ -13035,7 +13035,7 @@
         <v>1256.11</v>
       </c>
       <c r="D630" t="n">
-        <v>7445.45</v>
+        <v>226.63</v>
       </c>
       <c r="E630" t="n">
         <v>356.39</v>
@@ -13055,7 +13055,7 @@
         <v>1272.51</v>
       </c>
       <c r="D631" t="n">
-        <v>7495.99</v>
+        <v>226.23</v>
       </c>
       <c r="E631" t="n">
         <v>354.36</v>
@@ -13075,7 +13075,7 @@
         <v>1267.43</v>
       </c>
       <c r="D632" t="n">
-        <v>7873.81</v>
+        <v>225.33</v>
       </c>
       <c r="E632" t="n">
         <v>351.11</v>
@@ -13095,7 +13095,7 @@
         <v>1249.99</v>
       </c>
       <c r="D633" t="n">
-        <v>7699.77</v>
+        <v>225.91</v>
       </c>
       <c r="E633" t="n">
         <v>355.13</v>
@@ -13115,7 +13115,7 @@
         <v>1312.9</v>
       </c>
       <c r="D634" t="n">
-        <v>7701.93</v>
+        <v>227.13</v>
       </c>
       <c r="E634" t="n">
         <v>350.72</v>
@@ -13135,7 +13135,7 @@
         <v>1324.25</v>
       </c>
       <c r="D635" t="n">
-        <v>7689.84</v>
+        <v>224.04</v>
       </c>
       <c r="E635" t="n">
         <v>353.64</v>
@@ -13155,7 +13155,7 @@
         <v>1317.53</v>
       </c>
       <c r="D636" t="n">
-        <v>7611.32</v>
+        <v>224.78</v>
       </c>
       <c r="E636" t="n">
         <v>361.03</v>
@@ -13175,7 +13175,7 @@
         <v>1314.58</v>
       </c>
       <c r="D637" t="n">
-        <v>7630.01</v>
+        <v>233.01</v>
       </c>
       <c r="E637" t="n">
         <v>360.45</v>
@@ -13195,7 +13195,7 @@
         <v>1308.93</v>
       </c>
       <c r="D638" t="n">
-        <v>7888.3</v>
+        <v>255.67</v>
       </c>
       <c r="E638" t="n">
         <v>362.99</v>
@@ -13215,7 +13215,7 @@
         <v>1314.74</v>
       </c>
       <c r="D639" t="n">
-        <v>7907.56</v>
+        <v>260.22</v>
       </c>
       <c r="E639" t="n">
         <v>362.25</v>
@@ -13235,7 +13235,7 @@
         <v>1351.68</v>
       </c>
       <c r="D640" t="n">
-        <v>8698.32</v>
+        <v>259.14</v>
       </c>
       <c r="E640" t="n">
         <v>363.87</v>
@@ -13255,7 +13255,7 @@
         <v>1451.01</v>
       </c>
       <c r="D641" t="n">
-        <v>9568.15</v>
+        <v>262.24</v>
       </c>
       <c r="E641" t="n">
         <v>374.15</v>
@@ -13275,7 +13275,7 @@
         <v>1450.74</v>
       </c>
       <c r="D642" t="n">
-        <v>9037.58</v>
+        <v>267.08</v>
       </c>
       <c r="E642" t="n">
         <v>369.51</v>
@@ -13295,7 +13295,7 @@
         <v>1428.69</v>
       </c>
       <c r="D643" t="n">
-        <v>8950.559999999999</v>
+        <v>270.48</v>
       </c>
       <c r="E643" t="n">
         <v>369.99</v>
@@ -13315,7 +13315,7 @@
         <v>1451.89</v>
       </c>
       <c r="D644" t="n">
-        <v>8851.360000000001</v>
+        <v>277.09</v>
       </c>
       <c r="E644" t="n">
         <v>377.97</v>
@@ -13335,7 +13335,7 @@
         <v>1488.7</v>
       </c>
       <c r="D645" t="n">
-        <v>8762.790000000001</v>
+        <v>271.54</v>
       </c>
       <c r="E645" t="n">
         <v>382.17</v>
@@ -13355,7 +13355,7 @@
         <v>1465.86</v>
       </c>
       <c r="D646" t="n">
-        <v>8758.059999999999</v>
+        <v>269.5</v>
       </c>
       <c r="E646" t="n">
         <v>387.02</v>
@@ -13375,7 +13375,7 @@
         <v>1470.91</v>
       </c>
       <c r="D647" t="n">
-        <v>8654.09</v>
+        <v>262.58</v>
       </c>
       <c r="E647" t="n">
         <v>393.46</v>
@@ -13395,7 +13395,7 @@
         <v>1484.11</v>
       </c>
       <c r="D648" t="n">
-        <v>8394.940000000001</v>
+        <v>263.57</v>
       </c>
       <c r="E648" t="n">
         <v>410.12</v>
@@ -13415,7 +13415,7 @@
         <v>1481.65</v>
       </c>
       <c r="D649" t="n">
-        <v>8351.57</v>
+        <v>259.71</v>
       </c>
       <c r="E649" t="n">
         <v>424.77</v>
@@ -13435,7 +13435,7 @@
         <v>1467.01</v>
       </c>
       <c r="D650" t="n">
-        <v>8378.620000000001</v>
+        <v>258.27</v>
       </c>
       <c r="E650" t="n">
         <v>426.16</v>
@@ -13455,7 +13455,7 @@
         <v>1462.22</v>
       </c>
       <c r="D651" t="n">
-        <v>8356.790000000001</v>
+        <v>260.97</v>
       </c>
       <c r="E651" t="n">
         <v>413.55</v>
@@ -13475,7 +13475,7 @@
         <v>1479.65</v>
       </c>
       <c r="D652" t="n">
-        <v>8232.08</v>
+        <v>263.13</v>
       </c>
       <c r="E652" t="n">
         <v>409.19</v>
@@ -13495,7 +13495,7 @@
         <v>1472.15</v>
       </c>
       <c r="D653" t="n">
-        <v>8103.42</v>
+        <v>260.97</v>
       </c>
       <c r="E653" t="n">
         <v>396.42</v>
@@ -13515,7 +13515,7 @@
         <v>1470.4</v>
       </c>
       <c r="D654" t="n">
-        <v>8225.07</v>
+        <v>260.42</v>
       </c>
       <c r="E654" t="n">
         <v>391.24</v>
@@ -13535,7 +13535,7 @@
         <v>1495.23</v>
       </c>
       <c r="D655" t="n">
-        <v>8287.139999999999</v>
+        <v>260.33</v>
       </c>
       <c r="E655" t="n">
         <v>394.97</v>
@@ -13555,7 +13555,7 @@
         <v>1644.75</v>
       </c>
       <c r="D656" t="n">
-        <v>8370.209999999999</v>
+        <v>261.24</v>
       </c>
       <c r="E656" t="n">
         <v>395</v>
@@ -13575,7 +13575,7 @@
         <v>1637.64</v>
       </c>
       <c r="D657" t="n">
-        <v>8516.379999999999</v>
+        <v>264.36</v>
       </c>
       <c r="E657" t="n">
         <v>390.93</v>
@@ -13595,7 +13595,7 @@
         <v>1620.83</v>
       </c>
       <c r="D658" t="n">
-        <v>8439.18</v>
+        <v>270.35</v>
       </c>
       <c r="E658" t="n">
         <v>391.64</v>
@@ -13615,7 +13615,7 @@
         <v>1579.65</v>
       </c>
       <c r="D659" t="n">
-        <v>8382.719999999999</v>
+        <v>269.32</v>
       </c>
       <c r="E659" t="n">
         <v>389.98</v>
@@ -13635,7 +13635,7 @@
         <v>1587.39</v>
       </c>
       <c r="D660" t="n">
-        <v>8414.950000000001</v>
+        <v>273.1</v>
       </c>
       <c r="E660" t="n">
         <v>388.59</v>
@@ -13655,7 +13655,7 @@
         <v>1618.05</v>
       </c>
       <c r="D661" t="n">
-        <v>8457.780000000001</v>
+        <v>270.39</v>
       </c>
       <c r="E661" t="n">
         <v>390.42</v>
@@ -13675,7 +13675,7 @@
         <v>1645.35</v>
       </c>
       <c r="D662" t="n">
-        <v>8417.620000000001</v>
+        <v>272.98</v>
       </c>
       <c r="E662" t="n">
         <v>391.65</v>
@@ -13695,7 +13695,7 @@
         <v>1641</v>
       </c>
       <c r="D663" t="n">
-        <v>8452.23</v>
+        <v>275</v>
       </c>
       <c r="E663" t="n">
         <v>394.03</v>
@@ -13715,7 +13715,7 @@
         <v>1634.03</v>
       </c>
       <c r="D664" t="n">
-        <v>8470.09</v>
+        <v>273.15</v>
       </c>
       <c r="E664" t="n">
         <v>406.35</v>
@@ -13735,7 +13735,7 @@
         <v>1623.53</v>
       </c>
       <c r="D665" t="n">
-        <v>8471.209999999999</v>
+        <v>272.92</v>
       </c>
       <c r="E665" t="n">
         <v>404.3</v>
@@ -13755,7 +13755,7 @@
         <v>1622.55</v>
       </c>
       <c r="D666" t="n">
-        <v>8363.889999999999</v>
+        <v>270.74</v>
       </c>
       <c r="E666" t="n">
         <v>408.31</v>
@@ -13775,7 +13775,7 @@
         <v>1620.68</v>
       </c>
       <c r="D667" t="n">
-        <v>8202.059999999999</v>
+        <v>267.58</v>
       </c>
       <c r="E667" t="n">
         <v>404.15</v>
@@ -13795,7 +13795,7 @@
         <v>1645.95</v>
       </c>
       <c r="D668" t="n">
-        <v>8371.33</v>
+        <v>268.52</v>
       </c>
       <c r="E668" t="n">
         <v>405.39</v>
@@ -13815,7 +13815,7 @@
         <v>1697.28</v>
       </c>
       <c r="D669" t="n">
-        <v>8368.33</v>
+        <v>272.19</v>
       </c>
       <c r="E669" t="n">
         <v>416.1</v>
@@ -13835,7 +13835,7 @@
         <v>1732.81</v>
       </c>
       <c r="D670" t="n">
-        <v>8350</v>
+        <v>270.4</v>
       </c>
       <c r="E670" t="n">
         <v>411.95</v>
@@ -13855,7 +13855,7 @@
         <v>1720.37</v>
       </c>
       <c r="D671" t="n">
-        <v>8425.780000000001</v>
+        <v>272.12</v>
       </c>
       <c r="E671" t="n">
         <v>412.57</v>
@@ -13875,7 +13875,7 @@
         <v>1712.5</v>
       </c>
       <c r="D672" t="n">
-        <v>8445.26</v>
+        <v>277.26</v>
       </c>
       <c r="E672" t="n">
         <v>411.95</v>
@@ -13895,7 +13895,7 @@
         <v>1719.67</v>
       </c>
       <c r="D673" t="n">
-        <v>8412.42</v>
+        <v>280.64</v>
       </c>
       <c r="E673" t="n">
         <v>405.76</v>
@@ -13915,7 +13915,7 @@
         <v>1711.29</v>
       </c>
       <c r="D674" t="n">
-        <v>8376.16</v>
+        <v>282.71</v>
       </c>
       <c r="E674" t="n">
         <v>402.7</v>
@@ -13935,7 +13935,7 @@
         <v>1703</v>
       </c>
       <c r="D675" t="n">
-        <v>8399.4</v>
+        <v>282.86</v>
       </c>
       <c r="E675" t="n">
         <v>400.29</v>
@@ -13955,7 +13955,7 @@
         <v>1715.57</v>
       </c>
       <c r="D676" t="n">
-        <v>8435</v>
+        <v>277.88</v>
       </c>
       <c r="E676" t="n">
         <v>404.15</v>
@@ -13975,7 +13975,7 @@
         <v>1720.35</v>
       </c>
       <c r="D677" t="n">
-        <v>8445</v>
+        <v>280.53</v>
       </c>
       <c r="E677" t="n">
         <v>411.45</v>
@@ -13995,7 +13995,7 @@
         <v>1712.47</v>
       </c>
       <c r="D678" t="n">
-        <v>8381.860000000001</v>
+        <v>281.5</v>
       </c>
       <c r="E678" t="n">
         <v>418.88</v>
@@ -14015,7 +14015,7 @@
         <v>1808.43</v>
       </c>
       <c r="D679" t="n">
-        <v>8378.219999999999</v>
+        <v>277.23</v>
       </c>
       <c r="E679" t="n">
         <v>435.98</v>
@@ -14035,7 +14035,7 @@
         <v>1887.89</v>
       </c>
       <c r="D680" t="n">
-        <v>8430.1</v>
+        <v>276.69</v>
       </c>
       <c r="E680" t="n">
         <v>445.83</v>
@@ -14055,7 +14055,7 @@
         <v>1900.27</v>
       </c>
       <c r="D681" t="n">
-        <v>8401.74</v>
+        <v>278.41</v>
       </c>
       <c r="E681" t="n">
         <v>484.37</v>
@@ -14075,7 +14075,7 @@
         <v>1980.06</v>
       </c>
       <c r="D682" t="n">
-        <v>8601.59</v>
+        <v>277.92</v>
       </c>
       <c r="E682" t="n">
         <v>459.3</v>
@@ -14095,7 +14095,7 @@
         <v>1952.89</v>
       </c>
       <c r="D683" t="n">
-        <v>8350.43</v>
+        <v>274.49</v>
       </c>
       <c r="E683" t="n">
         <v>450.52</v>
@@ -14115,7 +14115,7 @@
         <v>1912.88</v>
       </c>
       <c r="D684" t="n">
-        <v>8337.91</v>
+        <v>271.34</v>
       </c>
       <c r="E684" t="n">
         <v>444.8</v>
@@ -14135,7 +14135,7 @@
         <v>1922.04</v>
       </c>
       <c r="D685" t="n">
-        <v>8349.98</v>
+        <v>269.56</v>
       </c>
       <c r="E685" t="n">
         <v>442.39</v>
@@ -14155,7 +14155,7 @@
         <v>1902.94</v>
       </c>
       <c r="D686" t="n">
-        <v>8306.780000000001</v>
+        <v>267.53</v>
       </c>
       <c r="E686" t="n">
         <v>444.42</v>
@@ -14175,7 +14175,7 @@
         <v>1875.52</v>
       </c>
       <c r="D687" t="n">
-        <v>8304.42</v>
+        <v>263.97</v>
       </c>
       <c r="E687" t="n">
         <v>445.28</v>
@@ -14195,7 +14195,7 @@
         <v>1833.07</v>
       </c>
       <c r="D688" t="n">
-        <v>8135.86</v>
+        <v>252.84</v>
       </c>
       <c r="E688" t="n">
         <v>430.35</v>
@@ -14215,7 +14215,7 @@
         <v>1923.94</v>
       </c>
       <c r="D689" t="n">
-        <v>8202.139999999999</v>
+        <v>264.23</v>
       </c>
       <c r="E689" t="n">
         <v>449.27</v>
@@ -14235,7 +14235,7 @@
         <v>1907.27</v>
       </c>
       <c r="D690" t="n">
-        <v>8335</v>
+        <v>260.64</v>
       </c>
       <c r="E690" t="n">
         <v>458.36</v>
@@ -14255,7 +14255,7 @@
         <v>1901.1</v>
       </c>
       <c r="D691" t="n">
-        <v>8178.57</v>
+        <v>258.88</v>
       </c>
       <c r="E691" t="n">
         <v>454.39</v>
@@ -14275,7 +14275,7 @@
         <v>1905.88</v>
       </c>
       <c r="D692" t="n">
-        <v>8133.19</v>
+        <v>258.21</v>
       </c>
       <c r="E692" t="n">
         <v>454.02</v>
@@ -14295,7 +14295,7 @@
         <v>1889.45</v>
       </c>
       <c r="D693" t="n">
-        <v>8131.16</v>
+        <v>263.9</v>
       </c>
       <c r="E693" t="n">
         <v>460.67</v>
@@ -14315,7 +14315,7 @@
         <v>1888.46</v>
       </c>
       <c r="D694" t="n">
-        <v>8144.19</v>
+        <v>264.63</v>
       </c>
       <c r="E694" t="n">
         <v>458.23</v>
@@ -14335,7 +14335,7 @@
         <v>1898.15</v>
       </c>
       <c r="D695" t="n">
-        <v>8158.71</v>
+        <v>266.92</v>
       </c>
       <c r="E695" t="n">
         <v>454.7</v>
@@ -14355,7 +14355,7 @@
         <v>1887.63</v>
       </c>
       <c r="D696" t="n">
-        <v>8123.24</v>
+        <v>266.32</v>
       </c>
       <c r="E696" t="n">
         <v>452.35</v>
@@ -14375,7 +14375,7 @@
         <v>1880</v>
       </c>
       <c r="D697" t="n">
-        <v>8113.57</v>
+        <v>264.27</v>
       </c>
       <c r="E697" t="n">
         <v>442.74</v>
@@ -14395,7 +14395,7 @@
         <v>1838.24</v>
       </c>
       <c r="D698" t="n">
-        <v>8051.11</v>
+        <v>260.76</v>
       </c>
       <c r="E698" t="n">
         <v>438.9</v>
@@ -14415,7 +14415,7 @@
         <v>1822.4</v>
       </c>
       <c r="D699" t="n">
-        <v>8000.02</v>
+        <v>255.89</v>
       </c>
       <c r="E699" t="n">
         <v>430.89</v>
@@ -14435,7 +14435,7 @@
         <v>1791.81</v>
       </c>
       <c r="D700" t="n">
-        <v>7957.11</v>
+        <v>256.58</v>
       </c>
       <c r="E700" t="n">
         <v>428.04</v>
@@ -14455,7 +14455,7 @@
         <v>1792.07</v>
       </c>
       <c r="D701" t="n">
-        <v>7925.51</v>
+        <v>253.8</v>
       </c>
       <c r="E701" t="n">
         <v>425.71</v>
@@ -14475,7 +14475,7 @@
         <v>1846.24</v>
       </c>
       <c r="D702" t="n">
-        <v>8076.29</v>
+        <v>256.67</v>
       </c>
       <c r="E702" t="n">
         <v>454.47</v>
@@ -14495,7 +14495,7 @@
         <v>1837.61</v>
       </c>
       <c r="D703" t="n">
-        <v>8055.1</v>
+        <v>257.32</v>
       </c>
       <c r="E703" t="n">
         <v>440.97</v>
@@ -14515,7 +14515,7 @@
         <v>1815.85</v>
       </c>
       <c r="D704" t="n">
-        <v>8051.77</v>
+        <v>254.16</v>
       </c>
       <c r="E704" t="n">
         <v>436.05</v>
@@ -14535,7 +14535,7 @@
         <v>1790.94</v>
       </c>
       <c r="D705" t="n">
-        <v>8004.72</v>
+        <v>250.87</v>
       </c>
       <c r="E705" t="n">
         <v>426.46</v>
@@ -14555,7 +14555,7 @@
         <v>1777.75</v>
       </c>
       <c r="D706" t="n">
-        <v>8034.4</v>
+        <v>248.3</v>
       </c>
       <c r="E706" t="n">
         <v>421.9</v>
@@ -14575,7 +14575,7 @@
         <v>1786.22</v>
       </c>
       <c r="D707" t="n">
-        <v>8027.15</v>
+        <v>246.04</v>
       </c>
       <c r="E707" t="n">
         <v>426.87</v>
@@ -14595,7 +14595,7 @@
         <v>1803.05</v>
       </c>
       <c r="D708" t="n">
-        <v>8038.53</v>
+        <v>252.65</v>
       </c>
       <c r="E708" t="n">
         <v>426.41</v>
@@ -14615,7 +14615,7 @@
         <v>1759.61</v>
       </c>
       <c r="D709" t="n">
-        <v>8003.75</v>
+        <v>243.21</v>
       </c>
       <c r="E709" t="n">
         <v>420.16</v>
@@ -14635,7 +14635,7 @@
         <v>1744.15</v>
       </c>
       <c r="D710" t="n">
-        <v>8003.97</v>
+        <v>240.15</v>
       </c>
       <c r="E710" t="n">
         <v>417.11</v>
@@ -14655,7 +14655,7 @@
         <v>1740.42</v>
       </c>
       <c r="D711" t="n">
-        <v>8021.65</v>
+        <v>243.15</v>
       </c>
       <c r="E711" t="n">
         <v>421.92</v>
@@ -14675,7 +14675,7 @@
         <v>1739.3</v>
       </c>
       <c r="D712" t="n">
-        <v>7987.38</v>
+        <v>247.42</v>
       </c>
       <c r="E712" t="n">
         <v>425.05</v>
@@ -14695,7 +14695,7 @@
         <v>1725.08</v>
       </c>
       <c r="D713" t="n">
-        <v>7998.37</v>
+        <v>246.34</v>
       </c>
       <c r="E713" t="n">
         <v>426.84</v>
@@ -14715,7 +14715,7 @@
         <v>1712.88</v>
       </c>
       <c r="D714" t="n">
-        <v>7989.99</v>
+        <v>245.42</v>
       </c>
       <c r="E714" t="n">
         <v>420.56</v>
@@ -14735,7 +14735,7 @@
         <v>1703.05</v>
       </c>
       <c r="D715" t="n">
-        <v>7999.5</v>
+        <v>251.29</v>
       </c>
       <c r="E715" t="n">
         <v>421.8</v>
@@ -14755,7 +14755,7 @@
         <v>1705.22</v>
       </c>
       <c r="D716" t="n">
-        <v>7995</v>
+        <v>255.4</v>
       </c>
       <c r="E716" t="n">
         <v>419.81</v>
@@ -14775,7 +14775,7 @@
         <v>1700.02</v>
       </c>
       <c r="D717" t="n">
-        <v>8049.33</v>
+        <v>254.04</v>
       </c>
       <c r="E717" t="n">
         <v>417.71</v>
@@ -14795,7 +14795,7 @@
         <v>1702.66</v>
       </c>
       <c r="D718" t="n">
-        <v>7996.56</v>
+        <v>250.79</v>
       </c>
       <c r="E718" t="n">
         <v>413.27</v>
@@ -14815,7 +14815,7 @@
         <v>1694.08</v>
       </c>
       <c r="D719" t="n">
-        <v>7963.2</v>
+        <v>249.4</v>
       </c>
       <c r="E719" t="n">
         <v>411.69</v>
@@ -14835,7 +14835,7 @@
         <v>1699.48</v>
       </c>
       <c r="D720" t="n">
-        <v>7944.49</v>
+        <v>253.62</v>
       </c>
       <c r="E720" t="n">
         <v>422.15</v>
@@ -14855,7 +14855,7 @@
         <v>1701.59</v>
       </c>
       <c r="D721" t="n">
-        <v>7944.7</v>
+        <v>260.28</v>
       </c>
       <c r="E721" t="n">
         <v>440.79</v>
@@ -14875,7 +14875,7 @@
         <v>1776.95</v>
       </c>
       <c r="D722" t="n">
-        <v>7999.46</v>
+        <v>265.21</v>
       </c>
       <c r="E722" t="n">
         <v>444.86</v>
@@ -14895,7 +14895,7 @@
         <v>1759.49</v>
       </c>
       <c r="D723" t="n">
-        <v>8000.28</v>
+        <v>271.07</v>
       </c>
       <c r="E723" t="n">
         <v>441.48</v>
@@ -14915,7 +14915,7 @@
         <v>1754.81</v>
       </c>
       <c r="D724" t="n">
-        <v>8006.13</v>
+        <v>267.39</v>
       </c>
       <c r="E724" t="n">
         <v>444.9</v>
@@ -14935,7 +14935,7 @@
         <v>1719.55</v>
       </c>
       <c r="D725" t="n">
-        <v>8001.23</v>
+        <v>269.34</v>
       </c>
       <c r="E725" t="n">
         <v>435.69</v>
@@ -14955,7 +14955,7 @@
         <v>1712.3</v>
       </c>
       <c r="D726" t="n">
-        <v>7955.25</v>
+        <v>270.67</v>
       </c>
       <c r="E726" t="n">
         <v>433.97</v>
@@ -14975,7 +14975,7 @@
         <v>1723.79</v>
       </c>
       <c r="D727" t="n">
-        <v>8030.25</v>
+        <v>274.58</v>
       </c>
       <c r="E727" t="n">
         <v>433.24</v>
@@ -14995,7 +14995,7 @@
         <v>1696.81</v>
       </c>
       <c r="D728" t="n">
-        <v>8004.98</v>
+        <v>274.36</v>
       </c>
       <c r="E728" t="n">
         <v>435.82</v>
@@ -15015,7 +15015,7 @@
         <v>1695.12</v>
       </c>
       <c r="D729" t="n">
-        <v>8033.77</v>
+        <v>272.4</v>
       </c>
       <c r="E729" t="n">
         <v>434.13</v>
@@ -15035,7 +15035,7 @@
         <v>1694.45</v>
       </c>
       <c r="D730" t="n">
-        <v>8043.5</v>
+        <v>270.21</v>
       </c>
       <c r="E730" t="n">
         <v>434.24</v>
@@ -15055,7 +15055,7 @@
         <v>1673.43</v>
       </c>
       <c r="D731" t="n">
-        <v>8000</v>
+        <v>272.83</v>
       </c>
       <c r="E731" t="n">
         <v>431.02</v>
@@ -15075,7 +15075,7 @@
         <v>1668.97</v>
       </c>
       <c r="D732" t="n">
-        <v>8000</v>
+        <v>275.11</v>
       </c>
       <c r="E732" t="n">
         <v>431.8</v>
@@ -15095,7 +15095,7 @@
         <v>1652.88</v>
       </c>
       <c r="D733" t="n">
-        <v>8001.07</v>
+        <v>278.67</v>
       </c>
       <c r="E733" t="n">
         <v>432</v>
@@ -15115,7 +15115,7 @@
         <v>1674.48</v>
       </c>
       <c r="D734" t="n">
-        <v>7950.97</v>
+        <v>275.6</v>
       </c>
       <c r="E734" t="n">
         <v>431.64</v>
@@ -15135,7 +15135,7 @@
         <v>1652.29</v>
       </c>
       <c r="D735" t="n">
-        <v>8000</v>
+        <v>271.33</v>
       </c>
       <c r="E735" t="n">
         <v>429.9</v>
@@ -15155,7 +15155,7 @@
         <v>1643.31</v>
       </c>
       <c r="D736" t="n">
-        <v>7984.98</v>
+        <v>269.29</v>
       </c>
       <c r="E736" t="n">
         <v>434.63</v>
@@ -15175,7 +15175,7 @@
         <v>1631.35</v>
       </c>
       <c r="D737" t="n">
-        <v>7982.8</v>
+        <v>267.99</v>
       </c>
       <c r="E737" t="n">
         <v>438.78</v>
@@ -15195,7 +15195,7 @@
         <v>1644.19</v>
       </c>
       <c r="D738" t="n">
-        <v>7997.86</v>
+        <v>266.87</v>
       </c>
       <c r="E738" t="n">
         <v>439.46</v>
@@ -15215,7 +15215,7 @@
         <v>1636.32</v>
       </c>
       <c r="D739" t="n">
-        <v>8005</v>
+        <v>264.84</v>
       </c>
       <c r="E739" t="n">
         <v>440.71</v>
@@ -15235,7 +15235,7 @@
         <v>1622.79</v>
       </c>
       <c r="D740" t="n">
-        <v>8010.51</v>
+        <v>267.46</v>
       </c>
       <c r="E740" t="n">
         <v>439.92</v>
@@ -15255,7 +15255,7 @@
         <v>1617.44</v>
       </c>
       <c r="D741" t="n">
-        <v>8006.08</v>
+        <v>270.4</v>
       </c>
       <c r="E741" t="n">
         <v>442.01</v>
@@ -15275,7 +15275,7 @@
         <v>1643.68</v>
       </c>
       <c r="D742" t="n">
-        <v>7968.91</v>
+        <v>273.57</v>
       </c>
       <c r="E742" t="n">
         <v>444</v>
@@ -15295,7 +15295,7 @@
         <v>1682.19</v>
       </c>
       <c r="D743" t="n">
-        <v>7948.59</v>
+        <v>280.71</v>
       </c>
       <c r="E743" t="n">
         <v>447.1</v>
@@ -15315,7 +15315,7 @@
         <v>1701.9</v>
       </c>
       <c r="D744" t="n">
-        <v>7952.62</v>
+        <v>281.09</v>
       </c>
       <c r="E744" t="n">
         <v>444.38</v>
@@ -15335,7 +15335,7 @@
         <v>1702.18</v>
       </c>
       <c r="D745" t="n">
-        <v>7998.75</v>
+        <v>287.82</v>
       </c>
       <c r="E745" t="n">
         <v>451.83</v>
@@ -15355,7 +15355,7 @@
         <v>1760.64</v>
       </c>
       <c r="D746" t="n">
-        <v>8010.16</v>
+        <v>294.24</v>
       </c>
       <c r="E746" t="n">
         <v>458.81</v>
@@ -15375,7 +15375,7 @@
         <v>1815.67</v>
       </c>
       <c r="D747" t="n">
-        <v>8021.43</v>
+        <v>295.48</v>
       </c>
       <c r="E747" t="n">
         <v>468.79</v>
@@ -15395,7 +15395,7 @@
         <v>1838.26</v>
       </c>
       <c r="D748" t="n">
-        <v>7998.12</v>
+        <v>293.45</v>
       </c>
       <c r="E748" t="n">
         <v>492.11</v>
@@ -15415,7 +15415,7 @@
         <v>1953.51</v>
       </c>
       <c r="D749" t="n">
-        <v>8014.85</v>
+        <v>295.87</v>
       </c>
       <c r="E749" t="n">
         <v>498.26</v>
@@ -15435,7 +15435,7 @@
         <v>1968.32</v>
       </c>
       <c r="D750" t="n">
-        <v>7981.09</v>
+        <v>296.11</v>
       </c>
       <c r="E750" t="n">
         <v>484.91</v>
@@ -15455,7 +15455,7 @@
         <v>1945.51</v>
       </c>
       <c r="D751" t="n">
-        <v>8000.96</v>
+        <v>293.11</v>
       </c>
       <c r="E751" t="n">
         <v>482.13</v>
@@ -15475,7 +15475,7 @@
         <v>1868.41</v>
       </c>
       <c r="D752" t="n">
-        <v>7999.99</v>
+        <v>289.88</v>
       </c>
       <c r="E752" t="n">
         <v>471.49</v>
@@ -15495,7 +15495,7 @@
         <v>1822.82</v>
       </c>
       <c r="D753" t="n">
-        <v>7990</v>
+        <v>294.58</v>
       </c>
       <c r="E753" t="n">
         <v>479.84</v>
@@ -15515,7 +15515,7 @@
         <v>1803.73</v>
       </c>
       <c r="D754" t="n">
-        <v>7950</v>
+        <v>303.25</v>
       </c>
       <c r="E754" t="n">
         <v>482.38</v>
@@ -15535,7 +15535,7 @@
         <v>1701.24</v>
       </c>
       <c r="D755" t="n">
-        <v>7998.98</v>
+        <v>308.2</v>
       </c>
       <c r="E755" t="n">
         <v>478.27</v>
@@ -15555,7 +15555,7 @@
         <v>1744.63</v>
       </c>
       <c r="D756" t="n">
-        <v>7952.25</v>
+        <v>329</v>
       </c>
       <c r="E756" t="n">
         <v>488.96</v>
@@ -15575,7 +15575,7 @@
         <v>1744.46</v>
       </c>
       <c r="D757" t="n">
-        <v>7996.47</v>
+        <v>328.98</v>
       </c>
       <c r="E757" t="n">
         <v>500.21</v>
@@ -15595,7 +15595,7 @@
         <v>1903.8</v>
       </c>
       <c r="D758" t="n">
-        <v>7988.51</v>
+        <v>333.9</v>
       </c>
       <c r="E758" t="n">
         <v>491.75</v>
@@ -15615,7 +15615,7 @@
         <v>1958.74</v>
       </c>
       <c r="D759" t="n">
-        <v>7925</v>
+        <v>331.26</v>
       </c>
       <c r="E759" t="n">
         <v>478.8</v>
@@ -15635,7 +15635,7 @@
         <v>1972.2</v>
       </c>
       <c r="D760" t="n">
-        <v>7988.79</v>
+        <v>332.49</v>
       </c>
       <c r="E760" t="n">
         <v>480.69</v>
@@ -15655,7 +15655,7 @@
         <v>1953.64</v>
       </c>
       <c r="D761" t="n">
-        <v>7764.52</v>
+        <v>327.85</v>
       </c>
       <c r="E761" t="n">
         <v>486.39</v>
@@ -15675,7 +15675,7 @@
         <v>2149</v>
       </c>
       <c r="D762" t="n">
-        <v>7970.64</v>
+        <v>327.47</v>
       </c>
       <c r="E762" t="n">
         <v>476.97</v>
@@ -15695,7 +15695,7 @@
         <v>2107.08</v>
       </c>
       <c r="D763" t="n">
-        <v>7900.83</v>
+        <v>330.12</v>
       </c>
       <c r="E763" t="n">
         <v>484.56</v>
@@ -15715,7 +15715,7 @@
         <v>2156.54</v>
       </c>
       <c r="D764" t="n">
-        <v>7905.39</v>
+        <v>333.56</v>
       </c>
       <c r="E764" t="n">
         <v>483.75</v>
@@ -15735,7 +15735,7 @@
         <v>2109.37</v>
       </c>
       <c r="D765" t="n">
-        <v>7857.86</v>
+        <v>321.81</v>
       </c>
       <c r="E765" t="n">
         <v>477.16</v>
@@ -15755,7 +15755,7 @@
         <v>2146.48</v>
       </c>
       <c r="D766" t="n">
-        <v>7883.79</v>
+        <v>323.93</v>
       </c>
       <c r="E766" t="n">
         <v>488.67</v>
@@ -15775,7 +15775,7 @@
         <v>2342.93</v>
       </c>
       <c r="D767" t="n">
-        <v>7774.41</v>
+        <v>328.97</v>
       </c>
       <c r="E767" t="n">
         <v>490.61</v>
@@ -15795,7 +15795,7 @@
         <v>2302.05</v>
       </c>
       <c r="D768" t="n">
-        <v>7830.74</v>
+        <v>329.02</v>
       </c>
       <c r="E768" t="n">
         <v>497.89</v>
@@ -15815,7 +15815,7 @@
         <v>2271.47</v>
       </c>
       <c r="D769" t="n">
-        <v>7906.13</v>
+        <v>328.8</v>
       </c>
       <c r="E769" t="n">
         <v>514.0599999999999</v>
@@ -15835,7 +15835,7 @@
         <v>2332.25</v>
       </c>
       <c r="D770" t="n">
-        <v>7852.73</v>
+        <v>321.18</v>
       </c>
       <c r="E770" t="n">
         <v>500.84</v>
@@ -15855,7 +15855,7 @@
         <v>2455.81</v>
       </c>
       <c r="D771" t="n">
-        <v>8265.26</v>
+        <v>310.07</v>
       </c>
       <c r="E771" t="n">
         <v>489.15</v>
@@ -15875,7 +15875,7 @@
         <v>2379.97</v>
       </c>
       <c r="D772" t="n">
-        <v>8178.65</v>
+        <v>308.05</v>
       </c>
       <c r="E772" t="n">
         <v>485.42</v>
@@ -15895,7 +15895,7 @@
         <v>2312.57</v>
       </c>
       <c r="D773" t="n">
-        <v>8097.09</v>
+        <v>306.32</v>
       </c>
       <c r="E773" t="n">
         <v>490.92</v>
@@ -15915,7 +15915,7 @@
         <v>2328.26</v>
       </c>
       <c r="D774" t="n">
-        <v>8012.5</v>
+        <v>300.47</v>
       </c>
       <c r="E774" t="n">
         <v>488.69</v>
@@ -15935,7 +15935,7 @@
         <v>2356.27</v>
       </c>
       <c r="D775" t="n">
-        <v>8013.14</v>
+        <v>294.74</v>
       </c>
       <c r="E775" t="n">
         <v>487.45</v>
@@ -15955,7 +15955,7 @@
         <v>2283.98</v>
       </c>
       <c r="D776" t="n">
-        <v>7955.26</v>
+        <v>285.41</v>
       </c>
       <c r="E776" t="n">
         <v>475</v>
@@ -15975,7 +15975,7 @@
         <v>2235.44</v>
       </c>
       <c r="D777" t="n">
-        <v>7966.5</v>
+        <v>293.6</v>
       </c>
       <c r="E777" t="n">
         <v>469.08</v>
@@ -15995,7 +15995,7 @@
         <v>2298.22</v>
       </c>
       <c r="D778" t="n">
-        <v>7999.56</v>
+        <v>297.49</v>
       </c>
       <c r="E778" t="n">
         <v>496.76</v>
@@ -16015,7 +16015,7 @@
         <v>2238.69</v>
       </c>
       <c r="D779" t="n">
-        <v>7952.26</v>
+        <v>283.67</v>
       </c>
       <c r="E779" t="n">
         <v>478.59</v>
@@ -16035,7 +16035,7 @@
         <v>2232.34</v>
       </c>
       <c r="D780" t="n">
-        <v>8046.98</v>
+        <v>290.41</v>
       </c>
       <c r="E780" t="n">
         <v>482.21</v>
@@ -16055,7 +16055,7 @@
         <v>2143.72</v>
       </c>
       <c r="D781" t="n">
-        <v>7996.45</v>
+        <v>284.85</v>
       </c>
       <c r="E781" t="n">
         <v>464.04</v>
@@ -16075,7 +16075,7 @@
         <v>2132.59</v>
       </c>
       <c r="D782" t="n">
-        <v>7904.29</v>
+        <v>285.57</v>
       </c>
       <c r="E782" t="n">
         <v>457.81</v>
@@ -16095,7 +16095,7 @@
         <v>2089.67</v>
       </c>
       <c r="D783" t="n">
-        <v>7979.5</v>
+        <v>282.01</v>
       </c>
       <c r="E783" t="n">
         <v>453.24</v>
@@ -16115,7 +16115,7 @@
         <v>2218.2</v>
       </c>
       <c r="D784" t="n">
-        <v>7903</v>
+        <v>287</v>
       </c>
       <c r="E784" t="n">
         <v>456.71</v>
@@ -16135,7 +16135,7 @@
         <v>2189.94</v>
       </c>
       <c r="D785" t="n">
-        <v>7998.89</v>
+        <v>283.47</v>
       </c>
       <c r="E785" t="n">
         <v>460.51</v>
@@ -16155,7 +16155,7 @@
         <v>1972.86</v>
       </c>
       <c r="D786" t="n">
-        <v>7667.2</v>
+        <v>255.12</v>
       </c>
       <c r="E786" t="n">
         <v>415.86</v>
@@ -16175,7 +16175,7 @@
         <v>2049.79</v>
       </c>
       <c r="D787" t="n">
-        <v>7796.18</v>
+        <v>260.35</v>
       </c>
       <c r="E787" t="n">
         <v>439</v>
@@ -16195,7 +16195,7 @@
         <v>2073.71</v>
       </c>
       <c r="D788" t="n">
-        <v>7800</v>
+        <v>263.56</v>
       </c>
       <c r="E788" t="n">
         <v>433.63</v>
@@ -16215,7 +16215,7 @@
         <v>2156.42</v>
       </c>
       <c r="D789" t="n">
-        <v>7830.4</v>
+        <v>285.28</v>
       </c>
       <c r="E789" t="n">
         <v>457.56</v>
@@ -16235,7 +16235,7 @@
         <v>2132.19</v>
       </c>
       <c r="D790" t="n">
-        <v>7770.19</v>
+        <v>275.79</v>
       </c>
       <c r="E790" t="n">
         <v>444.9</v>
@@ -16255,7 +16255,7 @@
         <v>1918.97</v>
       </c>
       <c r="D791" t="n">
-        <v>7713.65</v>
+        <v>272.48</v>
       </c>
       <c r="E791" t="n">
         <v>428.48</v>
@@ -16275,7 +16275,7 @@
         <v>1961.89</v>
       </c>
       <c r="D792" t="n">
-        <v>7899.29</v>
+        <v>288.6</v>
       </c>
       <c r="E792" t="n">
         <v>462.74</v>
@@ -16295,7 +16295,7 @@
         <v>1939.04</v>
       </c>
       <c r="D793" t="n">
-        <v>7814.28</v>
+        <v>283.27</v>
       </c>
       <c r="E793" t="n">
         <v>456.69</v>
@@ -16315,7 +16315,7 @@
         <v>1871.08</v>
       </c>
       <c r="D794" t="n">
-        <v>7821.88</v>
+        <v>274.81</v>
       </c>
       <c r="E794" t="n">
         <v>447.48</v>
@@ -16335,7 +16335,7 @@
         <v>1842.55</v>
       </c>
       <c r="D795" t="n">
-        <v>7799.67</v>
+        <v>273.09</v>
       </c>
       <c r="E795" t="n">
         <v>444.72</v>
@@ -16355,7 +16355,7 @@
         <v>1789.2</v>
       </c>
       <c r="D796" t="n">
-        <v>7781.36</v>
+        <v>261.86</v>
       </c>
       <c r="E796" t="n">
         <v>423.68</v>
@@ -16375,7 +16375,7 @@
         <v>1792.45</v>
       </c>
       <c r="D797" t="n">
-        <v>7892</v>
+        <v>262.64</v>
       </c>
       <c r="E797" t="n">
         <v>426.19</v>
@@ -16395,7 +16395,7 @@
         <v>1856.41</v>
       </c>
       <c r="D798" t="n">
-        <v>7899</v>
+        <v>279.75</v>
       </c>
       <c r="E798" t="n">
         <v>443.28</v>
@@ -16415,7 +16415,7 @@
         <v>1811.95</v>
       </c>
       <c r="D799" t="n">
-        <v>7887.17</v>
+        <v>276.61</v>
       </c>
       <c r="E799" t="n">
         <v>437.32</v>
@@ -16435,7 +16435,7 @@
         <v>1756.74</v>
       </c>
       <c r="D800" t="n">
-        <v>7700</v>
+        <v>276.5</v>
       </c>
       <c r="E800" t="n">
         <v>437.17</v>
@@ -16455,7 +16455,7 @@
         <v>1758.33</v>
       </c>
       <c r="D801" t="n">
-        <v>7700</v>
+        <v>281.64</v>
       </c>
       <c r="E801" t="n">
         <v>464.09</v>
@@ -16475,7 +16475,7 @@
         <v>1692.62</v>
       </c>
       <c r="D802" t="n">
-        <v>7748</v>
+        <v>274.13</v>
       </c>
       <c r="E802" t="n">
         <v>453.5</v>
@@ -16495,7 +16495,7 @@
         <v>1651.59</v>
       </c>
       <c r="D803" t="n">
-        <v>7742.38</v>
+        <v>265.62</v>
       </c>
       <c r="E803" t="n">
         <v>457.86</v>
@@ -16515,7 +16515,7 @@
         <v>1553</v>
       </c>
       <c r="D804" t="n">
-        <v>7532.62</v>
+        <v>263.5</v>
       </c>
       <c r="E804" t="n">
         <v>440.3</v>
@@ -16535,7 +16535,7 @@
         <v>1627.6</v>
       </c>
       <c r="D805" t="n">
-        <v>7712.4</v>
+        <v>270.64</v>
       </c>
       <c r="E805" t="n">
         <v>452.46</v>
@@ -16555,7 +16555,7 @@
         <v>1686.34</v>
       </c>
       <c r="D806" t="n">
-        <v>7697.29</v>
+        <v>279.08</v>
       </c>
       <c r="E806" t="n">
         <v>477.59</v>
@@ -16575,7 +16575,7 @@
         <v>1650.42</v>
       </c>
       <c r="D807" t="n">
-        <v>7696</v>
+        <v>271.47</v>
       </c>
       <c r="E807" t="n">
         <v>471.84</v>
@@ -16595,7 +16595,7 @@
         <v>1605.55</v>
       </c>
       <c r="D808" t="n">
-        <v>7677.46</v>
+        <v>270.59</v>
       </c>
       <c r="E808" t="n">
         <v>477.77</v>
